--- a/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
@@ -575,46 +575,46 @@
         <v>202</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.417452768898819</v>
+        <v>6.386099279704311</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.759907221550407</v>
+        <v>9.713978012110012</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.900837555974654</v>
+        <v>5.870426709370193</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.55598341198673</v>
+        <v>3.535101772237986</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.018040457399216</v>
+        <v>3.000824881011688</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.829925539458678</v>
+        <v>1.81721476444126</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.226461119134598</v>
+        <v>4.202821633529091</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.767949351169676</v>
+        <v>2.749970030746788</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.189456606655774</v>
+        <v>5.161927823797456</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.821869216760128</v>
+        <v>6.786868797004352</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.611600008233886</v>
+        <v>7.574398992796155</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.13394862245895</v>
+        <v>10.08509923409225</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.219695149488281</v>
+        <v>9.173778346983674</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.988007017038498</v>
+        <v>6.951784216238984</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>210</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.251980362687021</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.200524489312464</v>
+        <v>-2.196956497610564</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.119364862764002</v>
+        <v>-2.116526937117023</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.559039735329236</v>
+        <v>-0.563650238673695</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.482814123264944</v>
+        <v>-3.47196942706195</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.754340721339233</v>
+        <v>-1.75206105703699</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.978978357634787</v>
+        <v>1.962398606654503</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8749252815206958</v>
+        <v>-0.8784247577209712</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.9742003898076916</v>
+        <v>0.9624224124155987</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.078321895186896</v>
+        <v>1.065157627022664</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08292552346314608</v>
+        <v>-0.08942628027397603</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04662591152585804</v>
+        <v>-0.05480059132597148</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.9454864646930261</v>
+        <v>-0.9503631663086196</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.087059374688337</v>
+        <v>-3.081219084091479</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>193</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.270640392748838</v>
+        <v>-3.261653167388644</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.291893604210742</v>
+        <v>-2.28730234705673</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.131740388894002</v>
+        <v>-1.133460309748855</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5551860273549707</v>
+        <v>0.5442064796754806</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.610542361483482</v>
+        <v>2.592219784992665</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.910421645928352</v>
+        <v>2.889426483239212</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.7510567927749605</v>
+        <v>0.7380940880523426</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.322334395559345</v>
+        <v>1.307153444413494</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2229348153643613</v>
+        <v>0.2131131620482947</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4112403100100011</v>
+        <v>0.3993881464977846</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3149714406974908</v>
+        <v>-0.3213175630851168</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7988257988083376</v>
+        <v>-0.8044735095613547</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6993649706275846</v>
+        <v>-0.706254489925854</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4493976687518071</v>
+        <v>-0.4560031946265539</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>198</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.98838781515947</v>
+        <v>-1.98495602831008</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.579870211403538</v>
+        <v>-1.578429766141277</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.996941774297412</v>
+        <v>-3.983216117046069</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.878609935498901</v>
+        <v>-4.861571601263186</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.384665442423675</v>
+        <v>-2.378590394740975</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.123211795299817</v>
+        <v>-5.103570080402839</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.676853410835911</v>
+        <v>-2.673137730803241</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.159102367993448</v>
+        <v>-4.146697624026096</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.221395320904307</v>
+        <v>-4.208439936498863</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.07483857229397</v>
+        <v>-5.058529912522182</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.762018879814761</v>
+        <v>-3.750489038159238</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.741615040702811</v>
+        <v>-4.726549911404788</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.65671623940672</v>
+        <v>-4.643018020339994</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.424065442445794</v>
+        <v>-5.404451407323599</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4827521559804993</v>
+        <v>0.4721526766311328</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5332368564634251</v>
+        <v>-0.53774142513209</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.119684601003932</v>
+        <v>-2.114768376797613</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.18142302323853</v>
+        <v>-3.171578961516033</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.125862287057636</v>
+        <v>-3.114396772814679</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1544814339504157</v>
+        <v>0.1462044468802191</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6689269798503048</v>
+        <v>0.6534902934346576</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.380666916724408</v>
+        <v>4.344673085960217</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.919464436616913</v>
+        <v>4.880560954588255</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.265005241145531</v>
+        <v>5.222927991781738</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.66905668795706</v>
+        <v>2.644502865823981</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.305156117081594</v>
+        <v>3.275178433775714</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.688924070585614</v>
+        <v>1.667404209719749</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.939415295668645</v>
+        <v>1.918780915908734</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>218</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2588552577716712</v>
+        <v>0.247660047164743</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02412363309075261</v>
+        <v>0.01508604228763488</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3705789241313866</v>
+        <v>-0.376177690467479</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.049434738077075</v>
+        <v>-8.005744076900704</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.617660014539545</v>
+        <v>-2.607294874184177</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.699093578699049</v>
+        <v>-3.683706812915908</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.782873836924495</v>
+        <v>-3.772117360039928</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.173109942467626</v>
+        <v>-5.153450150378845</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6.617634977497715</v>
+        <v>-6.588442824652304</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.77687329416834</v>
+        <v>-9.728485052762771</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.145261376301185</v>
+        <v>-8.103665672958897</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-8.111940053052486</v>
+        <v>-8.07287088244518</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.614298060661213</v>
+        <v>-7.578988849169903</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.98314818028495</v>
+        <v>-5.95583682109433</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>141</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.953370190428238</v>
+        <v>4.90684213097169</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.344430877131607</v>
+        <v>3.310184981455762</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.211513261758931</v>
+        <v>7.151282689050433</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.083273731781588</v>
+        <v>3.056871909119991</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.124639896611413</v>
+        <v>1.110600466919088</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.269210671220513</v>
+        <v>4.231330676366696</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.478420515001922</v>
+        <v>3.439999777669456</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.876195707104344</v>
+        <v>0.8569727680227501</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.240309095818446</v>
+        <v>2.212644491422267</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.100411198532072</v>
+        <v>2.074365263000857</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.033200852787019</v>
+        <v>3.996911085472938</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.646002911586748</v>
+        <v>2.616724756668596</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.081659794721674</v>
+        <v>5.034203419469748</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.192068205867969</v>
+        <v>3.15991566768178</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>169</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.339592166363751</v>
+        <v>-6.30694270655799</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.731011232346653</v>
+        <v>-9.669943420029931</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.31579195063763</v>
+        <v>-11.24313766077333</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.857737571440332</v>
+        <v>-5.819517036496329</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.807085011752527</v>
+        <v>-5.769832455437282</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.477608648098801</v>
+        <v>-8.423403802793437</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-11.53292228490441</v>
+        <v>-11.46175149841746</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.255303251133327</v>
+        <v>-7.214866874819045</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6.725531682758422</v>
+        <v>-6.688615005600347</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.58369123996313</v>
+        <v>-7.53927121156736</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.414241300492797</v>
+        <v>-5.383804440937723</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.784245354002849</v>
+        <v>-4.761180805914002</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.226930132573855</v>
+        <v>-2.22636007676924</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1897145976202594</v>
+        <v>-0.2015346659452462</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>143</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.143787970559622</v>
+        <v>-2.140150167448539</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.357593883012449</v>
+        <v>-2.346755807843174</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6532381230812447</v>
+        <v>-0.6564144815627913</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.027005051370814</v>
+        <v>-3.99655084465337</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.971230459317503</v>
+        <v>-5.924980722892101</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.973901781486511</v>
+        <v>-4.938425698464023</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.46324903901376</v>
+        <v>-6.420659329579088</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.530494215981442</v>
+        <v>-5.496471422431668</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9.109504669778204</v>
+        <v>-9.044785734866942</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.63991013094946</v>
+        <v>-3.619957143467978</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3746243148348896</v>
+        <v>0.3620533569813347</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.699873391039802</v>
+        <v>-1.698326630076131</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.118602601032308</v>
+        <v>-2.11883725451402</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.869144861930472</v>
+        <v>-1.869097871970141</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>132</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.523741350513006</v>
+        <v>-5.487934764441874</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.074788457474497</v>
+        <v>-1.073754247631257</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.04716149076832465</v>
+        <v>0.03684218771813619</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.101175933201915</v>
+        <v>-2.082647905216653</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.162325570960078</v>
+        <v>-4.123804600484135</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.94776964993757</v>
+        <v>-9.859024987730336</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.515560032058914</v>
+        <v>-8.445488423551673</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.228271040049897</v>
+        <v>-8.162446265871033</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-12.10653527601438</v>
+        <v>-12.00118706051502</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.68099767495382</v>
+        <v>-10.59159500269809</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-13.94508968878284</v>
+        <v>-13.82688092678185</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.39036876336648</v>
+        <v>-12.28903546045226</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-14.34479304684431</v>
+        <v>-14.23130118200977</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.339529921352</v>
+        <v>-13.23273423560642</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>143</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.940990767762422</v>
+        <v>-4.90337313416854</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.557033187519778</v>
+        <v>-6.498938699209603</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.555832143006739</v>
+        <v>-5.51032919015546</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.578016981814457</v>
+        <v>1.562466620486234</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.844297624884874</v>
+        <v>3.808262905835022</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.549426635673449</v>
+        <v>5.49697610680731</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.364024647795986</v>
+        <v>3.326309247931036</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7886487865927876</v>
+        <v>0.7754319779590233</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7233347033597823</v>
+        <v>0.7187805660127324</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1293307990708001</v>
+        <v>-0.1297095737976974</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.451463303394902</v>
+        <v>-2.426483993913365</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2984406268057569</v>
+        <v>-0.3002400252262731</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.518794024011861</v>
+        <v>3.471985754004777</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.47911542814667</v>
+        <v>4.424608421736245</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>103</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.920622786229281</v>
+        <v>-4.875195288079105</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.594167381794357</v>
+        <v>-4.545826161381981</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.93796336563468</v>
+        <v>-6.867124676644913</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.947275953001991</v>
+        <v>-1.926333334950584</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.489418102890909</v>
+        <v>-2.461618101198063</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.142788486437709</v>
+        <v>-4.096980139121129</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.25239278939523</v>
+        <v>-3.223439693763417</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.725026109010706</v>
+        <v>-3.690087888348998</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.795217679006413</v>
+        <v>-3.749710249730263</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.63091225203133</v>
+        <v>-5.569234223712549</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-8.783925399152565</v>
+        <v>-8.682085171011352</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-11.69085320992935</v>
+        <v>-11.56436528292048</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-15.05793436261798</v>
+        <v>-14.90493148179591</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-15.800748209615</v>
+        <v>-15.63785338829839</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.809591982820244</v>
+        <v>3.008116606901545</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.63872983230663</v>
+        <v>4.909687735257457</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.172772787451791</v>
+        <v>6.544984902516639</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.443459812021608</v>
+        <v>4.702603619470487</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7.367716779336362</v>
+        <v>7.793172441047233</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.316914501640191</v>
+        <v>7.734392637319274</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.103256825189597</v>
+        <v>6.492382934631671</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>7.59242947937976</v>
+        <v>8.063644775474799</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.18968971307185</v>
+        <v>1.22498023444799</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3838963399915514</v>
+        <v>-0.4255519921475184</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.29400445378505</v>
+        <v>-1.432378659085344</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.054334266829066</v>
+        <v>-2.206402554750888</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.499260062571565</v>
+        <v>-2.629717188046037</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.492543463375732</v>
+        <v>-1.57584274000525</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1755575255079904</v>
+        <v>-0.1739419313223678</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.173133762190005</v>
+        <v>4.182656016337994</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.791510088705998</v>
+        <v>1.797003899603169</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.921763221313498</v>
+        <v>1.926660079383502</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.914671238791712</v>
+        <v>-3.921113848884431</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9682226785595702</v>
+        <v>-0.9688960624330463</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.688717985235897</v>
+        <v>-5.697597164373654</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.520139794613307</v>
+        <v>-1.520415209935351</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4056152860916953</v>
+        <v>0.4053886285061239</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.903061628145963</v>
+        <v>3.910145040148869</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.382534513532008</v>
+        <v>2.384644251686574</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.415808519978263</v>
+        <v>2.418998445939707</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.666889227114531</v>
+        <v>0.6682698876463462</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2517949519284599</v>
+        <v>0.2521142492421049</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.185193743821131</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.460644632482328</v>
+        <v>2.620673247519441</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.085977946087766</v>
+        <v>4.316515188509534</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>3.37958423186172</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.392897207083976</v>
+        <v>-3.527985661357455</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.095455269368315</v>
+        <v>-3.201438703025801</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.159986966438574</v>
+        <v>-1.18576009917259</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.637271375321077</v>
+        <v>-2.691022566593524</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.342132778900648</v>
+        <v>1.376039637934859</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.548396446531306</v>
+        <v>-3.689462699651976</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.193155363103614</v>
+        <v>-5.460700602420879</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.591232612990254</v>
+        <v>-4.808501939290799</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.466340661594394</v>
+        <v>-6.733029453990454</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.647623872718412</v>
+        <v>-5.888236627951038</v>
       </c>
     </row>
     <row r="21">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3158~3171</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3158</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.7432018017615434</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.01512</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2956~2969</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2956</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-1.230386787707452</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.03025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2746~2759</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2746</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.496700371677896</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.04537</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2553~2566</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2553</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-1.363274641332346</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.06049</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2355~2368</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2355</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.31100588777754</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.07561</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2187~2200</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2187</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.447983774755428</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.09074</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1969~1982</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1969</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.635718844932477</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.1059</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1828~1841</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1828</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-2.140369335962276</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.121</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1659~1672</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1659</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.715926358487486</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.1361</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1516~1529</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1516</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.675910524264914</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.1512</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1384~1397</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1384</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.312335958005249</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.1664</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1241~1254</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1241</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.8985419884715355</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.1815</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1138~1151</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1138</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.5386164262047686</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.1966</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1014~1019</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1014</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.9723392034288167</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.2117</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>864~868</t>
-        </is>
+      <c r="B20" t="n">
+        <v>864</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.110949840947299</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.2268</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>769~769</t>
-        </is>
+      <c r="B21" t="n">
+        <v>769</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.518145732433645</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.242</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>675~675</t>
-        </is>
+      <c r="B22" t="n">
+        <v>675</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.9378827646544181</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.2571</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>577~577</t>
-        </is>
+      <c r="B23" t="n">
+        <v>577</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.8469911798286986</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.2722</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>519~519</t>
-        </is>
+      <c r="B24" t="n">
+        <v>519</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.433708069728283</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.2873</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>452~452</t>
-        </is>
+      <c r="B25" t="n">
+        <v>452</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.608482567997584</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.3025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>396~396</t>
-        </is>
+      <c r="B26" t="n">
+        <v>396</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.9782868050584597</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.3176</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>359~359</t>
-        </is>
+      <c r="B27" t="n">
+        <v>359</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.239956426059557</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.3327</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>314~314</t>
-        </is>
+      <c r="B28" t="n">
+        <v>314</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.901081632311886</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.3478</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>257~257</t>
-        </is>
+      <c r="B29" t="n">
+        <v>257</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.7424655575640529</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.3629</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>227~227</t>
-        </is>
+      <c r="B30" t="n">
+        <v>227</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.3699978031380411</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.3781</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>205~205</t>
-        </is>
+      <c r="B31" t="n">
+        <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.677293387107099</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.3932</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>183~183</t>
-        </is>
+      <c r="B32" t="n">
+        <v>183</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.05847424809604</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.4083</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>154~154</t>
-        </is>
+      <c r="B33" t="n">
+        <v>154</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.40266557589392</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.4234</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B34" t="n">
+        <v>121</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.052016225244564</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.4386</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.928248426777976</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B6" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr"/>
@@ -3993,10 +3931,8 @@
           <t>X &lt; 0.01512</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1133~1133</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1133</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3.375935024891525</v>
@@ -4047,10 +3983,8 @@
           <t>X &lt; 0.03025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1343~1343</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1343</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.202764211435593</v>
@@ -4101,10 +4035,8 @@
           <t>X &lt; 0.04537</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1536~1536</t>
-        </is>
+      <c r="B9" t="n">
+        <v>1536</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.389374179790025</v>
@@ -4155,10 +4087,8 @@
           <t>X &lt; 0.06049</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1734~1734</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1734</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.889491322235237</v>
@@ -4209,10 +4139,8 @@
           <t>X &lt; 0.07561</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1902~1902</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1902</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1.765236758654375</v>
@@ -4263,10 +4191,8 @@
           <t>X &lt; 0.09074</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2120~2120</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2120</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.610335264695678</v>
@@ -4317,10 +4243,8 @@
           <t>X &lt; 0.1059</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2261~2261</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2261</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.818812896066014</v>
@@ -4371,10 +4295,8 @@
           <t>X &lt; 0.121</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2430~2430</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2430</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.251417646868212</v>
@@ -4425,10 +4347,8 @@
           <t>X &lt; 0.1361</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2573~2573</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2573</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.062721804158471</v>
@@ -4479,10 +4399,8 @@
           <t>X &lt; 0.1512</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2705~2705</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2705</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.7413121418972324</v>
@@ -4533,10 +4451,8 @@
           <t>X &lt; 0.1664</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2848~2848</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2848</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.4559998820372115</v>
@@ -4587,10 +4503,8 @@
           <t>X &lt; 0.1815</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2951~2951</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2951</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.2683373490546757</v>
@@ -4641,10 +4555,8 @@
           <t>X &lt; 0.1966</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3075~3083</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3075</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3771422830984932</v>
@@ -4695,10 +4607,8 @@
           <t>X &lt; 0.2117</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3225~3234</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3225</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.351335953135731</v>
@@ -4749,10 +4659,8 @@
           <t>X &lt; 0.2268</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3320~3333</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3320</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4018512087429187</v>
@@ -4803,10 +4711,8 @@
           <t>X &lt; 0.242</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3414~3427</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3414</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.2348954994573731</v>
@@ -4857,10 +4763,8 @@
           <t>X &lt; 0.2571</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3512~3525</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3512</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.1874127436198165</v>
@@ -4911,10 +4815,8 @@
           <t>X &lt; 0.2722</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3570~3583</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3570</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.2556546186680606</v>
@@ -4965,10 +4867,8 @@
           <t>X &lt; 0.2873</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3637~3650</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3637</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.2462877071872853</v>
@@ -5019,10 +4919,8 @@
           <t>X &lt; 0.3025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3693~3706</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3693</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.1509221762821937</v>
@@ -5073,10 +4971,8 @@
           <t>X &lt; 0.3176</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3730~3743</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3730</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.1648571646951851</v>
@@ -5127,10 +5023,8 @@
           <t>X &lt; 0.3327</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3775~3788</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3775</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.1200780472662686</v>
@@ -5181,10 +5075,8 @@
           <t>X &lt; 0.3478</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3832~3845</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3832</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.09433801268989583</v>
@@ -5235,10 +5127,8 @@
           <t>X &lt; 0.3629</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3862~3875</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3862</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.02269071204808881</v>
@@ -5289,10 +5179,8 @@
           <t>X &lt; 0.3781</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3884~3897</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3884</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.008486237141831054</v>
@@ -5343,10 +5231,8 @@
           <t>X &lt; 0.3932</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3906~3919</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3906</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.005558759097446853</v>
@@ -5397,10 +5283,8 @@
           <t>X &lt; 0.4083</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3935~3948</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3935</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.0111688166638757</v>
@@ -5451,10 +5335,8 @@
           <t>X &lt; 0.4234</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3968~3981</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3968</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.01918561988342304</v>
@@ -5505,10 +5387,8 @@
           <t>X &lt; 0.4386</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4006</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.01769808632095504</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown Recovery-7-90 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown Recovery-7-90 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>202</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.386099279704311</v>
+        <v>6.39856071495425</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.713978012110012</v>
+        <v>9.726834068889247</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.870426709370193</v>
+        <v>5.883380013465995</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.535101772237986</v>
+        <v>3.548029793490024</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.000824881011688</v>
+        <v>3.013887986644782</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.81721476444126</v>
+        <v>1.830214687177374</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.202821633529091</v>
+        <v>4.215852257008578</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.749970030746788</v>
+        <v>2.763119403731217</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.161927823797456</v>
+        <v>5.175101260297154</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.786868797004352</v>
+        <v>6.800254113485849</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.574398992796155</v>
+        <v>7.587841431439678</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.08509923409225</v>
+        <v>10.09854225482272</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.173778346983674</v>
+        <v>9.187329660839595</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.951784216238984</v>
+        <v>6.941354580540725</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>210</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.251980362687021</v>
+        <v>2.264427327127926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.196956497610564</v>
+        <v>-2.184125027955716</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.116526937117023</v>
+        <v>-2.103591874657688</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.563650238673695</v>
+        <v>-0.5507343966642964</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.47196942706195</v>
+        <v>-3.458920500755525</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.75206105703699</v>
+        <v>-1.739070909252327</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.962398606654503</v>
+        <v>1.975422519424264</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8784247577209712</v>
+        <v>-0.8652825468014598</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.9624224124155987</v>
+        <v>0.9755898595937396</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.065157627022664</v>
+        <v>1.07853753419176</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08942628027397603</v>
+        <v>-0.07598864343485445</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.05480059132597148</v>
+        <v>-0.04136123594966534</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.9503631663086196</v>
+        <v>-0.9368137107931389</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.081219084091479</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>193</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.261653167388644</v>
+        <v>-3.249227951827613</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.28730234705673</v>
+        <v>-2.274483549086199</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.133460309748855</v>
+        <v>-1.120535066841711</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5442064796754806</v>
+        <v>0.5571142831549025</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.592219784992665</v>
+        <v>2.605266860290889</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.889426483239212</v>
+        <v>2.902413924279543</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.7380940880523426</v>
+        <v>0.7511105774422759</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.307153444413494</v>
+        <v>1.320291653655005</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2131131620482947</v>
+        <v>0.2262753872573739</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3993881464977846</v>
+        <v>0.4127639224788453</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3213175630851168</v>
+        <v>-0.307883038253955</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.8044735095613547</v>
+        <v>-0.7910363454616345</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.706254489925854</v>
+        <v>-0.6927060133826473</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4560031946265539</v>
+        <v>-0.4664328303249476</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>198</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.98495602831008</v>
+        <v>-1.97254448963362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.578429766141277</v>
+        <v>-1.565624767619575</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.983216117046069</v>
+        <v>-3.970309922614582</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.861571601263186</v>
+        <v>-4.848684696234749</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.378590394740975</v>
+        <v>-2.365560997553658</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.103570080402839</v>
+        <v>-5.090602389918296</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.673137730803241</v>
+        <v>-2.66013327643234</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.146697624026096</v>
+        <v>-4.133571890093691</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.208439936498863</v>
+        <v>-4.195287468711989</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.058529912522182</v>
+        <v>-5.045162671021231</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.750489038159238</v>
+        <v>-3.737060035945333</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.726549911404788</v>
+        <v>-4.713116606642117</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.643018020339994</v>
+        <v>-4.629471471445271</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.404451407323599</v>
+        <v>-5.414881043021751</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4721526766311328</v>
+        <v>0.4845521736899556</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.53774142513209</v>
+        <v>-0.5249513689472778</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.114768376797613</v>
+        <v>-2.101875592462569</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.171578961516033</v>
+        <v>-3.158704897625562</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.114396772814679</v>
+        <v>-3.101382635933277</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1462044468802191</v>
+        <v>0.159167426714788</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6534902934346576</v>
+        <v>0.6664891414450835</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.344673085960217</v>
+        <v>4.35779978024852</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.880560954588255</v>
+        <v>4.893714795138742</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.222927991781738</v>
+        <v>5.236297103065688</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.644502865823981</v>
+        <v>2.657930942575454</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.275178433775714</v>
+        <v>3.288611730106837</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.667404209719749</v>
+        <v>1.680950408232441</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210852</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>218</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.247660047164743</v>
+        <v>0.2600359424997336</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01508604228763488</v>
+        <v>0.02785488733164243</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.376177690467479</v>
+        <v>-0.363302695468029</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.005744076900704</v>
+        <v>-7.99290364742933</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.607294874184177</v>
+        <v>-2.594299207163864</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.683706812915908</v>
+        <v>-3.670766790645409</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.772117360039928</v>
+        <v>-3.759138806839154</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.153450150378845</v>
+        <v>-5.140347065341707</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6.588442824652304</v>
+        <v>-6.575311020260393</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.728485052762771</v>
+        <v>-9.715137085275458</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.103665672958897</v>
+        <v>-8.090251049335329</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-8.07287088244518</v>
+        <v>-8.059446690401536</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.578988849169903</v>
+        <v>-7.565446797147573</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.95583682109433</v>
+        <v>-5.966266456792695</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>141</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.90684213097169</v>
+        <v>4.91920867629613</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.310184981455762</v>
+        <v>3.322938977470493</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.151282689050433</v>
+        <v>7.164157026407821</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.056871909119991</v>
+        <v>3.069714578588055</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.110600466919088</v>
+        <v>1.123582837509211</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.231330676366696</v>
+        <v>4.244268438304744</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.439999777669456</v>
+        <v>3.45297560502236</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8569727680227501</v>
+        <v>0.8700703877016096</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.212644491422267</v>
+        <v>2.22577511722951</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.074365263000857</v>
+        <v>2.087714530174132</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.996911085472938</v>
+        <v>4.010327158337574</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.616724756668596</v>
+        <v>2.630149182609408</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.034203419469748</v>
+        <v>5.047746205163314</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.15991566768178</v>
+        <v>3.149486031983791</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>169</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.30694270655799</v>
+        <v>-6.294652346689752</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.669943420029931</v>
+        <v>-9.657270933636958</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.24313766077333</v>
+        <v>-11.23035524872766</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.819517036496329</v>
+        <v>-5.806729466497522</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.769832455437282</v>
+        <v>-5.756895216249198</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.423403802793437</v>
+        <v>-8.410519553591321</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-11.46175149841746</v>
+        <v>-11.44882788652595</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.214866874819045</v>
+        <v>-7.201801299468023</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6.688615005600347</v>
+        <v>-6.675511979811276</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.53927121156736</v>
+        <v>-7.525945381043051</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.383804440937723</v>
+        <v>-5.370405311497656</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.761180805914002</v>
+        <v>-4.747766422202147</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.22636007676924</v>
+        <v>-2.212821990138949</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2015346659452462</v>
+        <v>-0.2119643016434694</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>143</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.140150167448539</v>
+        <v>-2.127888141203314</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.346755807843174</v>
+        <v>-2.334101424080892</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6564144815627913</v>
+        <v>-0.6436359622196122</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.99655084465337</v>
+        <v>-3.983798504838106</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.924980722892101</v>
+        <v>-5.912083051957481</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.938425698464023</v>
+        <v>-4.925566349262525</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.420659329579088</v>
+        <v>-6.407754821769323</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.496471422431668</v>
+        <v>-5.483427551135314</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9.044785734866942</v>
+        <v>-9.031709355387761</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.619957143467978</v>
+        <v>-3.606642629435179</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3620533569813347</v>
+        <v>0.3754470769665161</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.698326630076131</v>
+        <v>-1.684917852640787</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.11883725451402</v>
+        <v>-2.105302818432286</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.869097871970141</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>132</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.487934764441874</v>
+        <v>-5.475746945082527</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.073754247631257</v>
+        <v>-1.061143666572555</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.03684218771813619</v>
+        <v>0.0495800019823065</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.082647905216653</v>
+        <v>-2.069933699255522</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.123804600484135</v>
+        <v>-4.110945136875408</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.859024987730336</v>
+        <v>-9.846225406019528</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.445488423551673</v>
+        <v>-8.432626500677955</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.162446265871033</v>
+        <v>-8.149440058691695</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-12.00118706051502</v>
+        <v>-11.98814613103733</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.59159500269809</v>
+        <v>-10.57831381327257</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-13.82688092678185</v>
+        <v>-13.81352154592436</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.28903546045226</v>
+        <v>-12.27564637831536</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-14.23130118200977</v>
+        <v>-14.21777734550759</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.23273423560642</v>
+        <v>-13.24316387130457</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>143</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.90337313416854</v>
+        <v>-4.891260048183085</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.498938699209603</v>
+        <v>-6.486435740853032</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.51032919015546</v>
+        <v>-5.497688180706895</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.562466620486234</v>
+        <v>1.575143571355575</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.808262905835022</v>
+        <v>3.821108378050155</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.49697610680731</v>
+        <v>5.509791670788445</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.326309247931036</v>
+        <v>3.339172650401359</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7754319779590233</v>
+        <v>0.7884288983986067</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7187805660127324</v>
+        <v>0.731820591343876</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1297095737976974</v>
+        <v>-0.1164335673189854</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.426483993913365</v>
+        <v>-2.413128959679028</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3002400252262731</v>
+        <v>-0.2868521611286994</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.471985754004777</v>
+        <v>3.485512384610345</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.424608421736245</v>
+        <v>4.414178786038093</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>103</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.875195288079105</v>
+        <v>-4.86317636352809</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.545826161381981</v>
+        <v>-4.533402336286457</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.867124676644913</v>
+        <v>-6.85458062713974</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.926333334950584</v>
+        <v>-1.913745514315131</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.461618101198063</v>
+        <v>-2.448867981752478</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.096980139121129</v>
+        <v>-4.084266049202689</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.223439693763417</v>
+        <v>-3.210651160377651</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.690087888348998</v>
+        <v>-3.6771499297056</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.749710249730263</v>
+        <v>-3.736721184189562</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.569234223712549</v>
+        <v>-5.556002712605768</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-8.682085171011352</v>
+        <v>-8.668767696291951</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-11.56436528292048</v>
+        <v>-11.55100860635009</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-14.90493148179591</v>
+        <v>-14.8914246813324</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-15.63785338829839</v>
+        <v>-15.64828302399654</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>124</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.008116606901545</v>
+        <v>3.023330358881651</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.909687735257457</v>
+        <v>4.495039954447606</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.544984902516639</v>
+        <v>6.13007556720558</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.702603619470487</v>
+        <v>4.284917243957331</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7.793172441047233</v>
+        <v>7.37290594742889</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.734392637319274</v>
+        <v>7.31524467416714</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.492382934631671</v>
+        <v>6.077591213661229</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>8.063644775474799</v>
+        <v>7.645446655300958</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.22498023444799</v>
+        <v>0.7906228235368857</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4255519921475184</v>
+        <v>-0.4123434141027005</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.432378659085344</v>
+        <v>-1.419076460671846</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.206402554750888</v>
+        <v>-2.193053353890186</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.629717188046037</v>
+        <v>-2.616212068548521</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.57584274000525</v>
+        <v>-1.586272375703494</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>150</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1739419313223678</v>
+        <v>-0.5022858687923275</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.182656016337994</v>
+        <v>4.201012266733542</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.797003899603169</v>
+        <v>1.813153324374866</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.926660079383502</v>
+        <v>1.942440076208442</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.921113848884431</v>
+        <v>-3.911688022251901</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9688960624330463</v>
+        <v>-0.95623832130876</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.697597164373654</v>
+        <v>-5.689609531473934</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.520415209935351</v>
+        <v>-1.507391729858384</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4053886285061239</v>
+        <v>0.4184577261903186</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.910145040148869</v>
+        <v>3.552524464306764</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.384644251686574</v>
+        <v>2.397910088311001</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.418998445939707</v>
+        <v>2.432325457098152</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6682698876463462</v>
+        <v>0.6817624600714396</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2521142492421049</v>
+        <v>0.2416846135439883</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.185193743821131</v>
+        <v>2.163381204488779</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.620673247519441</v>
+        <v>2.59232567978124</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.316515188509534</v>
+        <v>4.270086937115224</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.37958423186172</v>
+        <v>3.347844722792736</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.527985661357455</v>
+        <v>-3.480047364865179</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.201438703025801</v>
+        <v>-3.161071952741537</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.18576009917259</v>
+        <v>-1.166049209089145</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.691022566593524</v>
+        <v>-2.663983828298363</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.376039637934859</v>
+        <v>1.380496764794877</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.689462699651976</v>
+        <v>-3.639688928616479</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.460700602420879</v>
+        <v>-5.974526415601638</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.808501939290799</v>
+        <v>-5.32947111762526</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.733029453990454</v>
+        <v>-7.238910543996035</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.888236627951038</v>
+        <v>-5.383315386456147</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>94</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.6849276819121</v>
+        <v>-5.672405392236477</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5.46945615193215</v>
+        <v>5.482365961508201</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.883098083633428</v>
+        <v>1.89610521505103</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.077181003474983</v>
+        <v>3.090160145873448</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.602589575636848</v>
+        <v>3.615700380011788</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.772371938884419</v>
+        <v>1.785414835178784</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.942957370548321</v>
+        <v>5.956023624848797</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.348114397298787</v>
+        <v>3.361295406594024</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.223284723882394</v>
+        <v>2.236483462837157</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.564648900556591</v>
+        <v>4.578054028209422</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.359895576239012</v>
+        <v>4.37335286994923</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.458108520818477</v>
+        <v>5.471560809538587</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.974024122639541</v>
+        <v>3.987580168991144</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.096085880447795</v>
+        <v>2.085656244749643</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>98</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.47303015694461</v>
+        <v>-1.460507867268987</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.125420096439477</v>
+        <v>-5.112510286863426</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6021601765556994</v>
+        <v>0.6151673079733015</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.328811180632705</v>
+        <v>-2.315832038234241</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.275624747152264</v>
+        <v>4.288735551527203</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.593474848133283</v>
+        <v>5.606517744427649</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.488332967595646</v>
+        <v>4.501399221896122</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.041557732079397</v>
+        <v>5.054738741374635</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.939741519366478</v>
+        <v>2.952940258321242</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.905271173286337</v>
+        <v>2.918728466996555</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.939654330631768</v>
+        <v>2.953106619351878</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.539807882952175</v>
+        <v>3.553363929303778</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.769121051963154</v>
+        <v>2.758691416265002</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>58</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.403113403927861</v>
+        <v>4.415635693603484</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.051604777701861</v>
+        <v>-1.038597646284259</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.251062148008998</v>
+        <v>4.264041290407462</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.712640932936914</v>
+        <v>3.725751737311853</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.010082870652489</v>
+        <v>4.023125766946855</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.925349153380211</v>
+        <v>3.938415407680687</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.162523900573511</v>
+        <v>-5.149342891278273</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.3971658684167</v>
+        <v>3.410364607371463</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8229027523539969</v>
+        <v>0.836307880006828</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.514701152174446</v>
+        <v>7.528158445884664</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.376670516416333</v>
+        <v>2.390122805136443</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.956415905471516</v>
+        <v>1.969971951823119</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4819993067133339</v>
+        <v>0.4715696710151818</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>67</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2546323500607244</v>
+        <v>-0.2421100603851016</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.118868663840608</v>
+        <v>1.131778473416659</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.201611897542605</v>
+        <v>5.214619028960207</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8542530898517313</v>
+        <v>0.8672322322501955</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.793443815077936</v>
+        <v>4.806554619452875</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.090885752793596</v>
+        <v>5.103928649087962</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.021077408655735</v>
+        <v>2.034143662956211</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.04643132330699</v>
+        <v>3.059612332602228</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.477968750557437</v>
+        <v>4.4911674895122</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.612918192395348</v>
+        <v>6.626323320048179</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.900702181510525</v>
+        <v>7.914159475220742</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.4425480254232</v>
+        <v>6.45600031414331</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.529756101045379</v>
+        <v>4.543312147396982</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.272014746754508</v>
+        <v>6.261585111056355</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>56</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.234808420621704</v>
+        <v>2.247919224996643</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.317964644051642</v>
+        <v>4.331007540346008</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6618023553507939</v>
+        <v>0.6748686096512699</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>7.350657108721627</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>9.997779599644687</v>
+        <v>10.01118472729752</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.235054997608799</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>16.97026657552972</v>
+        <v>16.98371886424983</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.77785372522214</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.00358937544868</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>37</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.651744823582526</v>
+        <v>2.664654633158577</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.959578819688637</v>
+        <v>4.97258595110624</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.387129249593357</v>
+        <v>2.400108391991822</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.254113439926591</v>
+        <v>7.267224244301531</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5565527304658531</v>
+        <v>-0.5435098341714877</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.749394555846237</v>
+        <v>-8.736328301545761</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-11.91928065733037</v>
+        <v>-11.90609964803513</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-17.38568594891807</v>
+        <v>-17.37248720996331</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.425000323135116</v>
+        <v>-7.411595195482285</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.224348242047363</v>
+        <v>-2.210890948337145</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.595370490107335</v>
+        <v>-7.581918201387225</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.09248300705586843</v>
+        <v>0.1060390534074713</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.360498363370546</v>
+        <v>-2.370927999068698</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>45</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.60454943132109</v>
+        <v>-3.592027141645467</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.216123044285347</v>
+        <v>-5.203213234709295</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.388769528659715</v>
+        <v>-3.375762397242113</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.702960840496658</v>
+        <v>-7.689981698098194</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-14.90804872223549</v>
+        <v>-14.89493791786055</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-12.38838456229761</v>
+        <v>-12.37534166600324</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-14.69534050179211</v>
+        <v>-14.68227424749163</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.71807945612917</v>
+        <v>-10.70489844683393</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.334634897867026</v>
+        <v>-6.321436158912263</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-13.85142674956162</v>
+        <v>-13.83802162190879</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.611735629434754</v>
+        <v>-9.598278335724537</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.577352472089323</v>
+        <v>-9.563900183369213</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-12.21982930525645</v>
+        <v>-12.20627325890484</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-9.747885750757938</v>
+        <v>-9.75831538645609</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>57</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.616245337753888</v>
+        <v>-1.603723048078265</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.982204915630376</v>
+        <v>-4.969295106054325</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-10.64023151696381</v>
+        <v>-10.62722438554621</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.755592419444028</v>
+        <v>-8.742613277045564</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.276469774867117</v>
+        <v>-2.263358970492177</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.487799766975925</v>
+        <v>-5.47475687068156</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.445010375400926</v>
+        <v>1.458076629701402</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7765589882929049</v>
+        <v>-0.7633779789976671</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>2.684411794304118</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.442070024415465</v>
+        <v>-3.428664896762633</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.646823348732944</v>
+        <v>-3.633366055022726</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.366826156299901</v>
+        <v>-5.353373867579791</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.541466732157076</v>
+        <v>-7.527910685805473</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.537359434968458</v>
+        <v>-5.54778907066661</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>30</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-9.160104986876547</v>
+        <v>-9.147582697200924</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-10.77167859984095</v>
+        <v>-10.7587687902649</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.036294173830036</v>
+        <v>-1.023315031431572</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.425284611097894</v>
+        <v>8.438395415472833</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.277273451186545</v>
+        <v>-1.26423055489218</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15.30465949820775</v>
+        <v>15.31772575250822</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.170809432759718</v>
+        <v>8.183990442054956</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>18.10980954657742</v>
+        <v>18.12300828553218</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.92635102821626</v>
+        <v>3.939756155869091</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.721597703898489</v>
+        <v>3.735054997608707</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.244019138755888</v>
+        <v>-6.230566850035778</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.66427374970079</v>
+        <v>-6.650717703349187</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-13.08121908409127</v>
+        <v>-13.09164871978942</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>22</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.19592102408326</v>
+        <v>-13.18301121450721</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-13.59078973067991</v>
+        <v>-13.57778259926231</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.915082052617805</v>
+        <v>-8.902102910219341</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.453503267689975</v>
+        <v>-9.440392463315035</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-13.70151587542899</v>
+        <v>-13.68847297913462</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1498859563374992</v>
+        <v>-0.1368197020370232</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.82385684155597</v>
+        <v>-10.81039954784575</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-19.88038277511956</v>
+        <v>-19.86693048639945</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-29.39154647697355</v>
+        <v>-29.37799043062195</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-24.59637059924279</v>
+        <v>-24.60680023494094</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>22</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.650466478628779</v>
+        <v>-8.637556669052728</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-22.68169882158901</v>
+        <v>-22.6686916901714</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-18.00599114352703</v>
+        <v>-17.99301200112856</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-18.5444123585992</v>
+        <v>-18.53130155422426</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-13.70151587542892</v>
+        <v>-13.68847297913455</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-9.240795047246657</v>
+        <v>-9.227728792946181</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-9.755779593255696</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-10.61910351723839</v>
+        <v>-10.60569838958556</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.244019138756052</v>
+        <v>-6.230566850035942</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-15.75518284061005</v>
+        <v>-15.74162679425844</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-20.05091605378824</v>
+        <v>-20.06134568948639</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>29</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.7693003891754913</v>
+        <v>-0.7567780994998685</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-23.07052917455354</v>
+        <v>-23.05761936497749</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.775742708736338</v>
+        <v>-2.762735577318736</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.25106214800919</v>
+        <v>4.264041290407654</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2643650708680028</v>
+        <v>0.277475875242942</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5618070085836138</v>
+        <v>0.5748499048779792</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.419478432826594</v>
+        <v>-6.406412178526118</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.33493769367706</v>
+        <v>-10.32175668438182</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-13.84421344192832</v>
+        <v>-13.83101470297356</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-14.69433862695625</v>
+        <v>-14.68093349930342</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-14.89909195127383</v>
+        <v>-14.88563465756361</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.968157069790522</v>
+        <v>-7.954704781070411</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.940135818666405</v>
+        <v>-4.926579772314803</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.242138624321157</v>
+        <v>-1.252568260019309</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.978286805058417</v>
+        <v>-0.9657645153827943</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.470745642583303</v>
+        <v>3.483655452159354</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.07563821552837</v>
+        <v>-12.06263108411077</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.9453850829209</v>
+        <v>-11.93240594052244</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-15.5141093282961</v>
+        <v>-15.50099852392116</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.15606132997442</v>
+        <v>-9.143018433680055</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-24.39231019876181</v>
+        <v>-24.37924394446133</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-15.76858450663424</v>
+        <v>-15.755403497339</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.708372271604439</v>
+        <v>-3.695173532649676</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-13.64940654754146</v>
+        <v>-13.63600141988863</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.793553811252977</v>
+        <v>-7.780096517542759</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.81977671451357</v>
+        <v>-13.80632442579346</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-17.27033435576153</v>
+        <v>-17.25677830940993</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.99030999318218</v>
+        <v>-14.00073962888033</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>38</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1381406271584069</v>
+        <v>0.1506629168340297</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.789724908931063</v>
+        <v>3.802634718507115</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.499880639770836</v>
+        <v>-4.486873508353234</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.369627507163379</v>
+        <v>-4.356648364764915</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.539627669603917</v>
+        <v>-7.526516865228977</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-12.50534362662506</v>
+        <v>-12.49230073033069</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-12.59007734389738</v>
+        <v>-12.5770110895969</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-13.05726074267888</v>
+        <v>-13.04407973338364</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.223523786755855</v>
+        <v>-5.210325047801092</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.073648971783804</v>
+        <v>-6.060243844130973</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.646823348732958</v>
+        <v>-3.633366055022741</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.9808612440191098</v>
+        <v>-0.9674089552989997</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.401115854963983</v>
+        <v>-1.38755980861238</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.480184424680672</v>
+        <v>1.46975478898252</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown Recovery-7-90 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown Recovery-7-90 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.7432018017615434</v>
+        <v>-0.7469942146453263</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.7296176114076758</v>
+        <v>-0.7335401557646861</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.044531949332203</v>
+        <v>-1.048387703936818</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.213061850597661</v>
+        <v>-1.216856632357157</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9137323344868378</v>
+        <v>-0.9176651905878259</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.073019924128168</v>
+        <v>-1.076881854755307</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.172433708743135</v>
+        <v>-1.176272984067758</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.338250828512933</v>
+        <v>-1.342075908655936</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.097693878441021</v>
+        <v>-1.10160191252934</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.17168818747011</v>
+        <v>-1.175640619344406</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.8845395944247301</v>
+        <v>-0.8886009163696968</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.022500151414221</v>
+        <v>-1.026517498564829</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.266996130201051</v>
+        <v>-1.27097086790625</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.284723411724784</v>
+        <v>-1.280949131312049</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.230386787707452</v>
+        <v>-1.2351247847431</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.443286865788785</v>
+        <v>-1.448114248892892</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.517069719649484</v>
+        <v>-1.52191393962007</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.537530406691303</v>
+        <v>-1.542357835610829</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.181235906046616</v>
+        <v>-1.1862393339091</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.270525812859908</v>
+        <v>-1.27547282583086</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.539754946611545</v>
+        <v>-1.544622425629278</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.617621807393327</v>
+        <v>-1.622511976664804</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.525448812085195</v>
+        <v>-1.530379065356847</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.715540863675734</v>
+        <v>-1.720493759700069</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.46258614199531</v>
+        <v>-1.467647705093903</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.781544493725562</v>
+        <v>-1.78649790782567</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.980472599886888</v>
+        <v>-1.985403301726564</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.847570008764258</v>
+        <v>-1.84263507983902</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.496700371677896</v>
+        <v>-1.502655160969134</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.385650076756541</v>
+        <v>-1.391848408484009</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.471226305349347</v>
+        <v>-1.477446387250971</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.612007768411509</v>
+        <v>-1.618164505497539</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.006052351999557</v>
+        <v>-1.012499601459972</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.23370046643705</v>
+        <v>-1.240032127789895</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.807581693219639</v>
+        <v>-1.813719418152488</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.674151807550359</v>
+        <v>-1.680399919974342</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.715708446879503</v>
+        <v>-1.721952954777898</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.928194426329298</v>
+        <v>-1.93447139774787</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.567598367400073</v>
+        <v>-1.574035911482113</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.913597013574034</v>
+        <v>-1.919908428791793</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.059250087523971</v>
+        <v>-2.065564864921335</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.753226852967202</v>
+        <v>-1.747151692729602</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.363274641332346</v>
+        <v>-1.370670607861967</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.317487566702496</v>
+        <v>-1.325149668415008</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.496760514965828</v>
+        <v>-1.504417368002343</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.775011822418882</v>
+        <v>-1.782545400646292</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.278072141439232</v>
+        <v>-1.285886025546858</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.545397881747476</v>
+        <v>-1.553067401106027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.00002800179211</v>
+        <v>-2.007537816410029</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.89953054379361</v>
+        <v>-1.907155391278366</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.86152222303425</v>
+        <v>-1.869176161517444</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.104153469241794</v>
+        <v>-2.111846658829997</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.661813876696101</v>
+        <v>-1.66971621866027</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.997443796290234</v>
+        <v>-2.005214737359815</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.161532950953827</v>
+        <v>-2.169308701392339</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.851293506339601</v>
+        <v>-1.8439327187453</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.31100588777754</v>
+        <v>-1.320088677220724</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.295548477322939</v>
+        <v>-1.30493996143602</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.287708196829151</v>
+        <v>-1.297181915619809</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.515504885598844</v>
+        <v>-1.524864763750486</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.185544492117053</v>
+        <v>-1.195149334351044</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.246239454854155</v>
+        <v>-1.255770318005503</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.943435336677801</v>
+        <v>-1.95269320644212</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.710596751060685</v>
+        <v>-1.720045685520539</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.664201752857608</v>
+        <v>-1.673688029588533</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.85576003579402</v>
+        <v>-1.865328589893721</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.486205519171818</v>
+        <v>-1.495975099890138</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.76799028852264</v>
+        <v>-1.77764064138448</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.952898537476777</v>
+        <v>-1.962554784384494</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.552556663709105</v>
+        <v>-1.543827553971646</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.447983774755428</v>
+        <v>-1.458653422628849</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.353761364734034</v>
+        <v>-1.364829396325462</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.224175453237613</v>
+        <v>-1.235395563832988</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.388289318724546</v>
+        <v>-1.399414515811266</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.037374769594322</v>
+        <v>-1.048784071706706</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.353203595453778</v>
+        <v>-1.364412704254605</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.142924822667226</v>
+        <v>-2.153800443391404</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.175747794782453</v>
+        <v>-2.186717549436985</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.166954443690216</v>
+        <v>-2.177949306807072</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.399527566033044</v>
+        <v>-2.410608807634659</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.803516451352564</v>
+        <v>-1.814922181761347</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.155394195859685</v>
+        <v>-2.166639909396608</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.231001354819718</v>
+        <v>-2.242312038662213</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.819216340607042</v>
+        <v>-1.808894301751643</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.635718844932477</v>
+        <v>-1.648843413287757</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.505314810508906</v>
+        <v>-1.518943697765692</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.318062457952635</v>
+        <v>-1.331901272108894</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6556305389975776</v>
+        <v>-0.6697796778961731</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8635593390201279</v>
+        <v>-0.8777575237221029</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.095179369244157</v>
+        <v>-1.109191795202214</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.962546979524902</v>
+        <v>-1.976153863070792</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.846068204371072</v>
+        <v>-1.859869207067838</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.677424495975764</v>
+        <v>-1.691337706028996</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.588093979386471</v>
+        <v>-1.602290450007402</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.105988502997974</v>
+        <v>-1.120494926364849</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.5002342579848</v>
+        <v>-1.514542509265091</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.638893039040987</v>
+        <v>-1.653254486707993</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.361225855718153</v>
+        <v>-1.348839921143053</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.140369335962276</v>
+        <v>-2.155183131511549</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.876751063609021</v>
+        <v>-1.892210760208719</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.971332515790401</v>
+        <v>-1.98687350835322</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9419887694048938</v>
+        <v>-0.9580621766191229</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.015833153373215</v>
+        <v>-1.03204346737089</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.506031621121139</v>
+        <v>-1.521897040103525</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.379264207514183</v>
+        <v>-2.394692548145223</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.054563159025079</v>
+        <v>-2.070323817708896</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.977479051349469</v>
+        <v>-1.993313052163195</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.870592203224888</v>
+        <v>-1.886757755751304</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.499592902327521</v>
+        <v>-1.516036705447966</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.817789630559268</v>
+        <v>-1.8340622077639</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.153612186004885</v>
+        <v>-2.169843386409397</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.70995723142898</v>
+        <v>-1.695621746944511</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.715926358487486</v>
+        <v>-1.733755241532563</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.082869503491402</v>
+        <v>-1.101671501588612</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.026826747555248</v>
+        <v>-1.045820246833173</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4451218151321683</v>
+        <v>-0.4644327959025816</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.531549921276266</v>
+        <v>-0.5510194037802592</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8013686321503073</v>
+        <v>-0.8205854709592799</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.454043983184668</v>
+        <v>-1.472916119117308</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.528890266939975</v>
+        <v>-1.547902315047878</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.497562248294372</v>
+        <v>-1.51663135410746</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.293131834080896</v>
+        <v>-1.312647690284855</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.103913728111046</v>
+        <v>-1.123634118446518</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.517950505402588</v>
+        <v>-1.537426055812048</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.146201460544262</v>
+        <v>-2.165467853861024</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.863618119654866</v>
+        <v>-1.846668800110706</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.675910524264914</v>
+        <v>-1.696602305044159</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9636506766297259</v>
+        <v>-0.9854964990069419</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.061766690851371</v>
+        <v>-1.083732147096676</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1101255412393414</v>
+        <v>-0.1326797989495319</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.02280282059614791</v>
+        <v>-0.04565875665478814</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4111317189030359</v>
+        <v>-0.433629461995956</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9855571794020932</v>
+        <v>-1.00773356507694</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.154639537892933</v>
+        <v>-1.176920041639505</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7856539642707077</v>
+        <v>-0.8082225510863026</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.073648971783832</v>
+        <v>-1.096404264906816</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.242194264501684</v>
+        <v>-1.264945002391194</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.500936134803425</v>
+        <v>-1.523522742070114</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.148782648843941</v>
+        <v>-2.171139310727412</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.863101230089512</v>
+        <v>-1.843571374151104</v>
       </c>
     </row>
     <row r="16">
@@ -2734,101 +2734,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.312335958005249</v>
+        <v>-1.336423898917758</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9531494689908442</v>
+        <v>-0.9782868050584526</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.191744568525138</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.07800520445790937</v>
+        <v>0.0519537857727741</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3683331873122455</v>
+        <v>0.3417909200160594</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4899679281238463</v>
+        <v>0.4634554944019555</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2740608468675916</v>
+        <v>-0.3000903394456529</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.486264907767854</v>
+        <v>-0.5123910580648499</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2840356084924736</v>
+        <v>0.2573008514794211</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1658679919567447</v>
+        <v>-0.1927132465788119</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.04192068110502589</v>
+        <v>-0.06897958452376685</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4720133667502182</v>
+        <v>-0.498771608507397</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9964037135998041</v>
+        <v>-1.023012075643663</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7787142671355838</v>
+        <v>-0.7571120170216687</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.1664</t>
+          <t>X &gt; 0.1663</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8985419884715355</v>
+        <v>-0.9271311699765832</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3141100975796576</v>
+        <v>-0.3440957440128614</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6660148250743276</v>
+        <v>-0.6959716727586454</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0930487701529259</v>
+        <v>-0.1234215277041599</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.02804872223549637</v>
+        <v>-0.05880682273665627</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.08698788940374413</v>
+        <v>-0.1175638882254688</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6889302453818544</v>
+        <v>-0.7191037110624947</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6316498027388064</v>
+        <v>-0.6621634040988909</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2339400976742709</v>
+        <v>0.2026661310280389</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1700345139525083</v>
+        <v>-0.2014958505515594</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2328517231911817</v>
+        <v>0.2009184514240587</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4918067493754563</v>
+        <v>-0.5231713516435903</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.511294683678344</v>
+        <v>-1.542109497395948</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.378291337650225</v>
+        <v>-1.352518285006809</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5386164262047686</v>
+        <v>-0.5711938083121311</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.06890111030402579</v>
+        <v>0.03474409707948922</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1047544430780434</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.07288120363807593</v>
+        <v>0.03847783192792065</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1922128296389616</v>
+        <v>0.157326890501821</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2759551701049503</v>
+        <v>0.2411457891938866</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4595326415301031</v>
+        <v>-0.4937925720989611</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3548315928812968</v>
+        <v>-0.3895175637674626</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5944989604006921</v>
+        <v>0.5589057214296247</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3186452488816585</v>
+        <v>0.2827132862276969</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.039739684617253</v>
+        <v>1.00300596083121</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.510366826156293</v>
+        <v>0.4740781981674473</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2990410894726168</v>
+        <v>-0.3349282296650813</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.08766313798699343</v>
+        <v>-0.05974939289448145</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9723392034288167</v>
+        <v>-1.010327795240237</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5230688517218312</v>
+        <v>-0.51015904214578</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9179375583184211</v>
+        <v>-0.9049304269008189</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4932781450435968</v>
+        <v>-0.4802990026451326</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7372930794484418</v>
+        <v>-0.7241822750735025</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6361219955109974</v>
+        <v>-0.623079099216632</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.309668274117925</v>
+        <v>-1.296602019817449</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.384309965342986</v>
+        <v>-1.371128956047748</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5173986862568398</v>
+        <v>0.530597425211603</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.4096516176071248</v>
+        <v>0.3676266171055005</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.342050014616376</v>
+        <v>1.298905685231588</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8425950344723603</v>
+        <v>0.7999149592069941</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.01402744428217062</v>
+        <v>-0.0562295143729088</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.09432332222036877</v>
+        <v>0.126742084808285</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.110949840947299</v>
+        <v>-1.098427551271676</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.340034974648887</v>
+        <v>-1.327125165072836</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.389281561429812</v>
+        <v>-1.376274430012209</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9134063090066391</v>
+        <v>-0.9004271666081749</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1845464180880256</v>
+        <v>-0.1714356137130864</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.578348720003703</v>
+        <v>-0.5653058237093376</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5478750640040886</v>
+        <v>-0.5348088097036126</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.360680582601255</v>
+        <v>-1.347499573306017</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5368448768385576</v>
+        <v>0.5500436157933208</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1980729349174837</v>
+        <v>-0.1846678072646526</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.161044070680589</v>
+        <v>1.108326887009724</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5689138866481684</v>
+        <v>0.5168379942547858</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1324818421864364</v>
+        <v>-0.1842050012707688</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.06692906405687182</v>
+        <v>0.1068098543916989</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>769</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.518145732433645</v>
+        <v>-1.505623442758022</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.829329228362788</v>
+        <v>-1.816419418786737</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.094158923255868</v>
+        <v>-2.081151791838266</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.443749743834324</v>
+        <v>-1.43077060143586</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2284922400531926</v>
+        <v>0.2416030444281319</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2542998924522095</v>
+        <v>-0.2412569961578441</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4690726214279977</v>
+        <v>-0.4560063671275216</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.196334043616517</v>
+        <v>-1.183153034321279</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4331732223468165</v>
+        <v>0.4463719613015797</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2332430958364426</v>
+        <v>0.2466482234892737</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.979074947071531</v>
+        <v>1.992532240781749</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.233224034195899</v>
+        <v>1.246676322916009</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6829304115474883</v>
+        <v>0.6964864578990912</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8026127321202665</v>
+        <v>0.7921830964221144</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>675</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9378827646544181</v>
+        <v>-0.9253604749787954</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.845752673914973</v>
+        <v>-2.832842864338922</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.648028787918975</v>
+        <v>-2.635021656501372</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.073331210867025</v>
+        <v>-2.060352068468561</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2413820555688275</v>
+        <v>-0.2282712511938882</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5365327104457549</v>
+        <v>-0.5234898141513895</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1838836206514927</v>
+        <v>0.1970823596062559</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3699452680801372</v>
+        <v>-0.3565401404273061</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.647523629824505</v>
+        <v>1.660980923534723</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.6448697501328979</v>
+        <v>0.658322038853008</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2246151391879962</v>
+        <v>0.2381711855395992</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6224846196124361</v>
+        <v>0.6120549839142839</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>577</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8469911798286986</v>
+        <v>-0.8344688901530759</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.458564792792956</v>
+        <v>-2.445654983216905</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.200053949996125</v>
+        <v>-3.187046818578523</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.029939465568866</v>
+        <v>-2.016960323170402</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.0085686529114</v>
+        <v>-0.9954578485364607</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.577677841712209</v>
+        <v>-1.564634945417843</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.355652460197653</v>
+        <v>-2.342586205897177</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.996146084282444</v>
+        <v>-2.982965074987206</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.284182365612061</v>
+        <v>-0.2709836266572978</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6143768747301124</v>
+        <v>-0.6009717470772813</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.433902729895117</v>
+        <v>1.447360023605334</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2551143101174986</v>
+        <v>0.2685665988376087</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3384505261306998</v>
+        <v>-0.3248944797790969</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2578912567521741</v>
+        <v>0.2474616210540219</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>519</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.433708069728283</v>
+        <v>-1.42118578005266</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.27456877325131</v>
+        <v>-2.261658963675259</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.44015038928913</v>
+        <v>-3.427143257871528</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.731862574600697</v>
+        <v>-2.718883432202233</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.536179743430097</v>
+        <v>-1.523068939055158</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.202128942515976</v>
+        <v>-2.189086046221611</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.057575569229485</v>
+        <v>-3.044509314929009</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.754046058569756</v>
+        <v>-2.740865049274518</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6955854437886728</v>
+        <v>-0.6823867048339096</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.7749977193753566</v>
+        <v>-0.7615925917225255</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.7543530025498342</v>
+        <v>0.7678102962600519</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.01802325045403563</v>
+        <v>0.03147553917414569</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.594909587851177</v>
+        <v>-0.5813535414995741</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2328464265060362</v>
+        <v>0.222416790807884</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>452</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.608482567997584</v>
+        <v>-1.595960278321961</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.777578304855645</v>
+        <v>-2.764668495279594</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.72111957782392</v>
+        <v>-4.708112446406318</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.26343281689784</v>
+        <v>-3.250453674499376</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.474420403651422</v>
+        <v>-2.461309599276483</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.283173156201244</v>
+        <v>-3.270130259906878</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.810384749579718</v>
+        <v>-3.797318495279242</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.613851334201932</v>
+        <v>-3.600670324906694</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.462461839853255</v>
+        <v>-1.449263100898492</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.870109148774986</v>
+        <v>-1.856704021122155</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3049509686677894</v>
+        <v>-0.2914936749575716</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9342846254816521</v>
+        <v>-0.9208323367615421</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.354539236426554</v>
+        <v>-1.340983190074951</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6623400280440706</v>
+        <v>-0.6727696637422227</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>396</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.9782868050584597</v>
+        <v>-0.9657645153828369</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.762506902397085</v>
+        <v>-5.749499770979483</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.117102254638077</v>
+        <v>-4.104123112239613</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.140371954558731</v>
+        <v>-3.127261150183791</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.358081531994586</v>
+        <v>-4.34503863570022</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.442815249266864</v>
+        <v>-4.429748994966388</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.445746008978134</v>
+        <v>-2.43254727002337</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.548396446531306</v>
+        <v>-3.534991318878475</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.227897245596367</v>
+        <v>-1.214439951886149</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.466241360978209</v>
+        <v>-3.452789072258099</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.633970719397858</v>
+        <v>-3.620414673046255</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.879198882071066</v>
+        <v>-2.889628517769218</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>359</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.239956426059557</v>
+        <v>-1.227434136383934</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.8013907632578</v>
+        <v>-4.788480953681749</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.867568662054943</v>
+        <v>-6.854561530637341</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.787454805213464</v>
+        <v>-4.774475662815</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.211669892151924</v>
+        <v>-4.198559087776985</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.74988255053654</v>
+        <v>-4.736839654242175</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.998961671708543</v>
+        <v>-3.985895417408067</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.466145070490043</v>
+        <v>-4.452964061194805</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9059750402378057</v>
+        <v>-0.8927763012830425</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.148857885432861</v>
+        <v>-3.13545275778003</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.125198953483036</v>
+        <v>-1.111741659772818</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.040676520371591</v>
+        <v>-3.027224231651481</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.018034195383336</v>
+        <v>-4.004478149031733</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.932658267006772</v>
+        <v>-2.943087902704924</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>314</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.901081632311886</v>
+        <v>-0.8885593426362632</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.741954608333465</v>
+        <v>-4.729044798757414</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.366122677987384</v>
+        <v>-7.353115546569782</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.67874935917817</v>
+        <v>-2.66563855480323</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.655192771780975</v>
+        <v>-3.642149875486609</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.466041138734788</v>
+        <v>-2.452974884434312</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.570167212675521</v>
+        <v>-3.556986203380283</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1279823854820279</v>
+        <v>-0.1147836465272647</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.615050245669188</v>
+        <v>-1.601645118016357</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.09102445549093829</v>
+        <v>0.104481749201156</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.10389175022096</v>
+        <v>-2.09043946150085</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.842617698745478</v>
+        <v>-2.829061652393875</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.955953691309951</v>
+        <v>-1.966383327008103</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>257</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7424655575640529</v>
+        <v>-0.7299432678884301</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.688669520722868</v>
+        <v>-4.675759711146817</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.639958460782495</v>
+        <v>-6.626951329364893</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.396864861248929</v>
+        <v>-3.383885718850465</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.767970901223812</v>
+        <v>-2.754860096848873</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.24873908023968</v>
+        <v>-3.235696183945315</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.333472797511959</v>
+        <v>-3.320406543211483</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.189761254659217</v>
+        <v>-4.176580245363979</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7488156155496881</v>
+        <v>-0.7356168765949249</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.209835742211851</v>
+        <v>-1.19643061455902</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.920041283665114</v>
+        <v>0.9334985773753317</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.380205909183999</v>
+        <v>-1.366753620463889</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.800460520128901</v>
+        <v>-1.786904473777298</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.161634129486856</v>
+        <v>-1.172063765185008</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>227</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3699978031380411</v>
+        <v>0.3825200928136638</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.884747615993611</v>
+        <v>-3.87183780641756</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.363316763118839</v>
+        <v>-7.350309631701236</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.708834555621465</v>
+        <v>-3.695855413223001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.247255770693634</v>
+        <v>-4.234144966318695</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.509285198616752</v>
+        <v>-3.496242302322386</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-5.796662087695189</v>
+        <v>-5.783595833394713</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.823316852115461</v>
+        <v>-5.810135842820223</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.241144932130361</v>
+        <v>-3.227946193175598</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.888626945352122</v>
+        <v>-1.875221817699291</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5497915364977004</v>
+        <v>0.5632488302079182</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7374112092405696</v>
+        <v>-0.7239589205204595</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.157665820185471</v>
+        <v>-1.144109773833868</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4136414151745171</v>
+        <v>0.403211779476365</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.677293387107099</v>
+        <v>0.6898156767827217</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.885499738052282</v>
+        <v>-2.872589928476231</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.695002590990335</v>
+        <v>-6.681995459572732</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.150115312041372</v>
+        <v>-3.137136169642908</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.688536527113541</v>
+        <v>-3.675425722738602</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.415484833300319</v>
+        <v>-2.402441937005953</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.402657574962845</v>
+        <v>-6.389591320662369</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.382036095695561</v>
+        <v>-6.368855086400323</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.516206713585177</v>
+        <v>-3.503007974630414</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.927307508369204</v>
+        <v>-1.913902380716372</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.770378191703458</v>
+        <v>1.783835485413675</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.316956471000104</v>
+        <v>1.330408759720214</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.872311616152764</v>
+        <v>1.885867662504367</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.097642704526613</v>
+        <v>3.087213068828461</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>183</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.05847424809604</v>
+        <v>1.070996537771663</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.1924436271633</v>
+        <v>-2.179533817587249</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.773104683486672</v>
+        <v>-4.76009755206907</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.364163026288999</v>
+        <v>-1.351183883890535</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.902584241361168</v>
+        <v>-1.889473436986229</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.058694216213816</v>
+        <v>-1.04565131991945</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.061460720371343</v>
+        <v>-6.048394466070867</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-6.528644119152844</v>
+        <v>-6.515463109857606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.764507393313288</v>
+        <v>-2.751308654358525</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8823921411827484</v>
+        <v>-0.8689870135299174</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.191543059089838</v>
+        <v>2.205000352800056</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.225926216435269</v>
+        <v>2.239378505155379</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.991463955217142</v>
+        <v>4.005020001568745</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.880529549788513</v>
+        <v>5.87009991409036</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>154</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.40266557589392</v>
+        <v>1.415187865569543</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.73914391098161</v>
+        <v>1.752053720557662</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-5.149231289121474</v>
+        <v>-5.136224157703872</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.421575559111382</v>
+        <v>-2.408596416712918</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.310646124832893</v>
+        <v>-2.297535320457953</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.363853537766587</v>
+        <v>-1.350810641472222</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.994041800493406</v>
+        <v>-5.98097554619293</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.811874549924262</v>
+        <v>-5.798693540629024</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.718558820423958</v>
+        <v>1.731963948076789</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.409909392210274</v>
+        <v>5.423366685920492</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.145591250854409</v>
+        <v>4.159043539574519</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.673388587961448</v>
+        <v>5.686944634313051</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>121</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.266888893272053</v>
+        <v>1.279798702848105</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.260211218283224</v>
+        <v>-3.247204086865622</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.290298385202526</v>
+        <v>1.303409189577465</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.7612940419264547</v>
+        <v>0.7743369382208201</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.9763322373293022</v>
+        <v>-0.9632659830288262</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.096408198094267</v>
+        <v>-3.083227188799029</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1483770396903736</v>
+        <v>0.1615757786451368</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.90982210259633</v>
+        <v>5.923227230249161</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.010853902245699</v>
+        <v>9.024311195955917</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.04523705959113</v>
+        <v>9.058689348311241</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.93076757261317</v>
+        <v>11.94432361896477</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.00693518588119</v>
+        <v>12.99650555018304</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.928248426777976</v>
+        <v>2.940770716453599</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1118555367052849</v>
+        <v>0.1247653462813361</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.692651724108174</v>
+        <v>-2.679644592690572</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.256878516933071</v>
+        <v>2.269857659331535</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.332915133186198</v>
+        <v>5.346025937561137</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.835176348010286</v>
+        <v>6.848219244304651</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.340804076521145</v>
+        <v>4.353870330821621</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.463982123522783</v>
+        <v>1.477163132818021</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2.607801514448902</v>
+        <v>2.621000253403665</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>11.39623054628845</v>
+        <v>11.40963567394128</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.80593505329617</v>
+        <v>14.81939234700639</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.63549893353317</v>
+        <v>13.64895122225328</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>18.03452143102199</v>
+        <v>18.0480774773736</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.28424276329828</v>
+        <v>18.27381312760013</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown Recovery-7-90 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown Recovery-7-90 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3935,46 +3935,46 @@
         <v>1133</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.375935024891525</v>
+        <v>3.388457314567148</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.970892744672192</v>
+        <v>3.983802554248243</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.840807798004988</v>
+        <v>3.85381492942259</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.324105943851684</v>
+        <v>4.337085086250148</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.432639715540319</v>
+        <v>3.445750519915258</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.641820399946184</v>
+        <v>3.654863296240549</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.174915455842488</v>
+        <v>4.187981710142964</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.237299576919774</v>
+        <v>4.250480586215012</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.264560944047268</v>
+        <v>4.277759683002031</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.650093305356499</v>
+        <v>4.66349843300933</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.092294967799731</v>
+        <v>4.105752261509949</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.097551911552934</v>
+        <v>5.111004200273044</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.912954846945183</v>
+        <v>5.926510893296786</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.633108659362684</v>
+        <v>5.622679023664531</v>
       </c>
     </row>
     <row r="8">
@@ -3987,46 +3987,46 @@
         <v>1343</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.202764211435593</v>
+        <v>3.215286501111216</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.005933710906184</v>
+        <v>3.018843520482235</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.908905659559039</v>
+        <v>2.921912790976641</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.56037993885306</v>
+        <v>3.573359081251525</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.351817249469647</v>
+        <v>2.364928053844586</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.79817951481003</v>
+        <v>2.811222411104396</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.830348254723148</v>
+        <v>3.843414509023624</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.437625019754009</v>
+        <v>3.450806029049247</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.74892595263352</v>
+        <v>3.762124691588284</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.090163388603351</v>
+        <v>4.103568516256182</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.438649081411612</v>
+        <v>3.452106375121829</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.292094040693001</v>
+        <v>4.305546329413112</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.839821559308788</v>
+        <v>4.853377605660391</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.270481089649117</v>
+        <v>4.260051453950965</v>
       </c>
     </row>
     <row r="9">
@@ -4039,46 +4039,46 @@
         <v>1536</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.389374179790025</v>
+        <v>2.401896469465647</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.340300566825768</v>
+        <v>2.353210376401819</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.401161026895842</v>
+        <v>2.414168158313444</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.182455826170013</v>
+        <v>3.195434968568478</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.383617944431172</v>
+        <v>2.396728748806112</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.811268215480169</v>
+        <v>2.824311111774534</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.442680331541226</v>
+        <v>3.455746585841702</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.305122046577424</v>
+        <v>3.318320785532187</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.626871861549496</v>
+        <v>3.640276989202327</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.966389370565246</v>
+        <v>2.979846664275463</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.651814194577348</v>
+        <v>3.665266483297458</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.143017916965775</v>
+        <v>4.156573963317378</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.676593415908734</v>
+        <v>3.666163780210582</v>
       </c>
     </row>
     <row r="10">
@@ -4091,46 +4091,46 @@
         <v>1734</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.889491322235237</v>
+        <v>1.90201361191086</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.892681261750795</v>
+        <v>1.905591071326846</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.670822935777039</v>
+        <v>1.683830067194641</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.262437083378778</v>
+        <v>2.275416225777242</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.839356122055172</v>
+        <v>1.852466926430111</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.906117552273713</v>
+        <v>1.919160448568078</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.744105864989898</v>
+        <v>2.757172119290374</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.334592593082675</v>
+        <v>2.347773602377913</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.446603087523215</v>
+        <v>2.459801826477978</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.634540186232307</v>
+        <v>2.647945313885138</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.199106354417609</v>
+        <v>2.212563648127826</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.694850526757271</v>
+        <v>2.708302815477381</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.139647818926562</v>
+        <v>3.153203865278165</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.63965750183722</v>
+        <v>2.629227866139068</v>
       </c>
     </row>
     <row r="11">
@@ -4143,46 +4143,46 @@
         <v>1902</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.765236758654375</v>
+        <v>1.777759048329997</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.678373976394639</v>
+        <v>1.69128378597069</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.336081505339585</v>
+        <v>1.349088636757187</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.781792051196291</v>
+        <v>1.794771193594755</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.401099542748739</v>
+        <v>1.414210347123678</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.751117716005936</v>
+        <v>1.764160612300302</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.560180002939752</v>
+        <v>2.573246257240228</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.513606488490531</v>
+        <v>2.526787497785769</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.662911544474369</v>
+        <v>2.676110283429132</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.864311070277147</v>
+        <v>2.877716197929978</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.238947861627288</v>
+        <v>2.252405155337506</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.746517138846535</v>
+        <v>2.759969427566645</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.009753589941589</v>
+        <v>3.023309636293192</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.575983860177921</v>
+        <v>2.565554224479769</v>
       </c>
     </row>
     <row r="12">
@@ -4195,46 +4195,46 @@
         <v>2120</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.610335264695678</v>
+        <v>1.622857554371301</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.508195613995575</v>
+        <v>1.521105423571626</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.160496718719742</v>
+        <v>1.173503850137344</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7718819267989403</v>
+        <v>0.7848610691974045</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9881776928588479</v>
+        <v>1.001288497233787</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.191280007932995</v>
+        <v>1.204322904227361</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.90843308311355</v>
+        <v>1.921499337414026</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.724268552256582</v>
+        <v>1.73744956155182</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.71043847739503</v>
+        <v>1.723637216349793</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.56786046217843</v>
+        <v>1.581265589831261</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.174427892577832</v>
+        <v>1.18788518628805</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.633339351810044</v>
+        <v>1.646791640530154</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.92063191067647</v>
+        <v>1.934187957028072</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.698655129745205</v>
+        <v>1.688225494047053</v>
       </c>
     </row>
     <row r="13">
@@ -4247,46 +4247,46 @@
         <v>2261</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.818812896066014</v>
+        <v>1.831335185741636</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.622542246392328</v>
+        <v>1.635452055968379</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.537271063015559</v>
+        <v>1.550278194433162</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9156444963749308</v>
+        <v>0.928623638773395</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.996418327742397</v>
+        <v>1.009529132117336</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.382316700663715</v>
+        <v>1.39535959695808</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.005234465036722</v>
+        <v>2.018300719337198</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.670735719063721</v>
+        <v>1.683916728358959</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.742420485689912</v>
+        <v>1.755619224644676</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.599946782307271</v>
+        <v>1.613351909960102</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.350965240386856</v>
+        <v>1.364422534097073</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.694945920952101</v>
+        <v>1.708398209672211</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.115027444460978</v>
+        <v>2.128583490812581</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.789781947900472</v>
+        <v>1.77935231220232</v>
       </c>
     </row>
     <row r="14">
@@ -4299,46 +4299,46 @@
         <v>2430</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.251417646868212</v>
+        <v>1.263939936543835</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8332596717640399</v>
+        <v>0.8461694813400911</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6441522820398831</v>
+        <v>0.6571594134574852</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4451873076514943</v>
+        <v>0.4581664500499585</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5240500431966097</v>
+        <v>0.537160847571549</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6980351907888078</v>
+        <v>0.7110780870831732</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.065976370635873</v>
+        <v>1.079042624936349</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.05146786897371</v>
+        <v>1.064648878268947</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.155077036289356</v>
+        <v>1.168275775244119</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.9633880652531985</v>
+        <v>0.9767931929060296</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8820915310590749</v>
+        <v>0.8955488247692927</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.245692795400387</v>
+        <v>1.259145084120497</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.813092505443144</v>
+        <v>1.826648551794747</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.65129120397458</v>
+        <v>1.640861568276428</v>
       </c>
     </row>
     <row r="15">
@@ -4351,46 +4351,46 @@
         <v>2573</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.062721804158471</v>
+        <v>1.075244093834094</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6559674683026415</v>
+        <v>0.6688772778786927</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5720198654759727</v>
+        <v>0.5850269968935748</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1970262044573516</v>
+        <v>0.2100053468558158</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1638517830113031</v>
+        <v>0.1769625873862424</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3835634447844853</v>
+        <v>0.3966063410788507</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6486159692533633</v>
+        <v>0.6616822235538393</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6866793640979765</v>
+        <v>0.6998603733932143</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5868143399444392</v>
+        <v>0.6000130788992024</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7083176041975037</v>
+        <v>0.7217227318503348</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8533505216210813</v>
+        <v>0.866807815331299</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.082059368822719</v>
+        <v>1.095511657542829</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.594568069187559</v>
+        <v>1.608124115539162</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.455638021751462</v>
+        <v>1.445208386053309</v>
       </c>
     </row>
     <row r="16">
@@ -4403,98 +4403,98 @@
         <v>2705</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7413121418972324</v>
+        <v>0.7538344315728551</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5715130206150434</v>
+        <v>0.5844228301910945</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5463300811164231</v>
+        <v>0.5593372125340252</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.0850859863671829</v>
+        <v>0.0980651287656471</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.04668088489723488</v>
+        <v>-0.0335700805222956</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1189247142795296</v>
+        <v>-0.1058818179851642</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2029959122559433</v>
+        <v>0.2160621665564193</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2533725874116044</v>
+        <v>0.2665535967068422</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.02943875902947468</v>
+        <v>-0.01624002007471148</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1555562038169001</v>
+        <v>0.1689613314697311</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1356457630483021</v>
+        <v>0.1491030567585199</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4288089573623139</v>
+        <v>0.442261246082424</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8218630340329298</v>
+        <v>0.8354190803845327</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.738867175921051</v>
+        <v>0.7284375402228989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.1664</t>
+          <t>X &lt; 0.1663</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2848</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4559998820372115</v>
+        <v>0.4685221717128343</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2138082915448649</v>
+        <v>0.2267181011209161</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.240287899555014</v>
+        <v>0.2532950309726161</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1598668748591479</v>
+        <v>0.1728460172576121</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.148131053045411</v>
+        <v>0.1612418574203502</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.164674114356572</v>
+        <v>0.1777170106509374</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3608392734887929</v>
+        <v>0.3739055277892689</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2798918297634714</v>
+        <v>0.2930728390587092</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.00821778627779679</v>
+        <v>0.02141652523255999</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1412386686656006</v>
+        <v>0.1546437963184317</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.006710063449141046</v>
+        <v>0.0201673571593588</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3922168163001913</v>
+        <v>0.4056691050203014</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9551082727710209</v>
+        <v>0.9686643191226239</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9239307286428158</v>
+        <v>0.9135010929446636</v>
       </c>
     </row>
     <row r="18">
@@ -4507,46 +4507,46 @@
         <v>2951</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2683373490546757</v>
+        <v>0.2808596387302984</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04612327522970361</v>
+        <v>0.05903308480575475</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.009877251089015715</v>
+        <v>0.00312988032858641</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.08648906349068852</v>
+        <v>0.09946820588915273</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.05637011883533916</v>
+        <v>0.06948092321027843</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.01494387627312221</v>
+        <v>0.02798677256748761</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2351915212509255</v>
+        <v>0.2482577755514015</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1407631207750768</v>
+        <v>0.1539441300703146</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1235576735739343</v>
+        <v>-0.1103589346191711</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.05873877185161547</v>
+        <v>-0.04533364419878438</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2973789141969831</v>
+        <v>-0.2839216204867654</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.02578803065703994</v>
+        <v>-0.01233574193692988</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4011278090927348</v>
+        <v>0.4146838554443377</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3458677791189473</v>
+        <v>0.3354381434207951</v>
       </c>
     </row>
     <row r="19">
@@ -4559,46 +4559,46 @@
         <v>3075</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3771422830984932</v>
+        <v>0.3896645727741159</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.238095735629841</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2550690518877303</v>
+        <v>0.2503101386292599</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2732296356938164</v>
+        <v>0.2684733489644486</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3696388386609044</v>
+        <v>0.3648023418797095</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3276648204184411</v>
+        <v>0.3228648223948625</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4882799076976525</v>
+        <v>0.4834177603056418</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4616633556032355</v>
+        <v>0.4567669559754393</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.06905224204047045</v>
+        <v>-0.07378408551246451</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.07364897178383245</v>
+        <v>-0.06024384413100137</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3434429465079276</v>
+        <v>-0.3299856527977099</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1139378379429843</v>
+        <v>-0.1004855492228742</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2788156811934215</v>
+        <v>0.2923717275450244</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2683744118436877</v>
+        <v>0.2579447761455356</v>
       </c>
     </row>
     <row r="20">
@@ -4611,46 +4611,46 @@
         <v>3225</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.351335953135731</v>
+        <v>0.34752291846101</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4263830559999136</v>
+        <v>0.4224309623634781</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3268520334965075</v>
+        <v>0.322900695172919</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3502734522919582</v>
+        <v>0.3463219322648499</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1693506585694706</v>
+        <v>0.1654149140800243</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2670643210856198</v>
+        <v>0.2631172263256119</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.199331121504045</v>
+        <v>0.195396858113817</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.368929461682356</v>
+        <v>0.364907418510974</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.04683438811983365</v>
+        <v>-0.05073409645314797</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1123975398440678</v>
+        <v>0.1083860380760555</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2163867922254497</v>
+        <v>-0.2029294985152319</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.004042876747888613</v>
+        <v>0.01749516546799867</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2969665603766316</v>
+        <v>0.3105226067282345</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2676181252110581</v>
+        <v>0.257188489512906</v>
       </c>
     </row>
     <row r="21">
@@ -4660,49 +4660,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4018512087429187</v>
+        <v>0.3985080846426143</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4868248015196457</v>
+        <v>0.4833554221564</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4385762800730717</v>
+        <v>0.4350952791617857</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4351772976414878</v>
+        <v>0.4317034815275491</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.06341417953681372</v>
+        <v>0.0600170370944042</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1670374462493953</v>
+        <v>0.1636256581848698</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1588825219530108</v>
+        <v>0.1554661371237529</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2794484385725085</v>
+        <v>0.2759651940838168</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.005478673973954074</v>
+        <v>-0.008881872816182579</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.003366672018813688</v>
+        <v>-9.346819115307881e-05</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3650709689873608</v>
+        <v>-0.3684347737510052</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1332424981780207</v>
+        <v>-0.1366757877427673</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.09573829486399887</v>
+        <v>0.09220824487467638</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.09147167896094288</v>
+        <v>0.09413869364026795</v>
       </c>
     </row>
     <row r="22">
@@ -4712,49 +4712,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2348954994573731</v>
+        <v>0.2320361281587608</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6235344766331252</v>
+        <v>0.6204744740090504</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4782215500101969</v>
+        <v>0.4751813661359776</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5077089414348137</v>
+        <v>0.5046655038482797</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1606045059269405</v>
+        <v>0.1576321755973922</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2111348870172876</v>
+        <v>0.2081620831446784</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3178135467317205</v>
+        <v>0.3148034848286443</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3637918889000673</v>
+        <v>0.3607418792565582</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.05579765226134725</v>
+        <v>0.05283284693570067</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.128808605746876</v>
+        <v>0.1257754597590122</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2350894485743495</v>
+        <v>-0.2380286770547499</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.02061786358593309</v>
+        <v>0.01760406011922555</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2024905255553335</v>
+        <v>0.1993993926694486</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1466660945847664</v>
+        <v>0.1489564534658285</v>
       </c>
     </row>
     <row r="23">
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1874127436198165</v>
+        <v>0.1849943494996822</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4636600305034051</v>
+        <v>0.4610893657635273</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4816691757273333</v>
+        <v>0.4790742782529094</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.428782487158081</v>
+        <v>0.4262071560980445</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2751378724819205</v>
+        <v>0.2725805375625043</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3609841245710754</v>
+        <v>0.3584145269974854</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4339575942579046</v>
+        <v>0.431362116144733</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4940991807225785</v>
+        <v>0.4914641561782886</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.136157760016907</v>
+        <v>0.1336203757349494</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1550199701956814</v>
+        <v>0.1524374183085726</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1475345862863406</v>
+        <v>-0.1500417031875543</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1020252550971676</v>
+        <v>0.09944737471519005</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2955896149447099</v>
+        <v>0.2929362522568582</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2198439379284736</v>
+        <v>0.2217586243608807</v>
       </c>
     </row>
     <row r="24">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.2556546186680606</v>
+        <v>0.2534589694656475</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3896837675516167</v>
+        <v>0.3873843402589259</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4568353613461866</v>
+        <v>0.4545000259851335</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.490707688367408</v>
+        <v>0.4883669940734521</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3308448234476629</v>
+        <v>0.3285257692902874</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4201366475651298</v>
+        <v>0.417803532841873</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4905694786384132</v>
+        <v>0.4882120577067965</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4023530569207949</v>
+        <v>0.4000001336028092</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1890636258315013</v>
+        <v>0.1867666747939296</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1658585827768775</v>
+        <v>0.1635323796452113</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.02315460508546607</v>
+        <v>-0.02543744783048396</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1389595846482621</v>
+        <v>0.1366315826537345</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3225646709095855</v>
+        <v>0.320166955105357</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2241030447602697</v>
+        <v>0.2258160426487379</v>
       </c>
     </row>
     <row r="25">
@@ -4868,49 +4868,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3637</v>
+        <v>3638</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.2462877071872853</v>
+        <v>0.244364714467018</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4030724735125304</v>
+        <v>0.4010485613333188</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5439790093519861</v>
+        <v>0.5419014984979711</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4973864769331939</v>
+        <v>0.4953253194456764</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.412850893782057</v>
+        <v>0.4107928197319879</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5059912950412127</v>
+        <v>0.5039171869253849</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5187099921705638</v>
+        <v>0.5166283588183873</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4509814521576558</v>
+        <v>0.4489007969762966</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.267964406544472</v>
+        <v>0.2659307853034321</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2844943954229748</v>
+        <v>0.2824250191309403</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1226966049974791</v>
+        <v>0.1206633469633758</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.255019058550964</v>
+        <v>0.2529496334806041</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4000473058241241</v>
+        <v>0.3979220328419757</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.3355163205462617</v>
+        <v>0.336975066173558</v>
       </c>
     </row>
     <row r="26">
@@ -4920,49 +4920,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1509221762821937</v>
+        <v>0.1492431278147137</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.496877405557214</v>
+        <v>0.4950538397045676</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5757133127129777</v>
+        <v>0.5738552365860485</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5318037647783456</v>
+        <v>0.5299607065094349</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.4404115694987141</v>
+        <v>0.4385754496792771</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5636704378525081</v>
+        <v>0.5618094234979267</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5208757144241076</v>
+        <v>0.5190226992795033</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.5552376566040067</v>
+        <v>0.553359811424329</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.3470549044285107</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4316255751461</v>
+        <v>0.4297507475401687</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2151041974050756</v>
+        <v>0.2132805859236413</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5083489261966534</v>
+        <v>0.5064461369771109</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6178052974025192</v>
+        <v>0.6158587513191875</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.5580985438534896</v>
+        <v>0.5593168098983554</v>
       </c>
     </row>
     <row r="27">
@@ -4972,49 +4972,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3730</v>
+        <v>3731</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1648571646951851</v>
+        <v>0.1633147386964211</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5181842186162555</v>
+        <v>0.5165006014886515</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6190715120602377</v>
+        <v>0.6173488326409071</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.550158589093364</v>
+        <v>0.5484572219766548</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5078378784598812</v>
+        <v>0.5061316008560226</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5525820865342084</v>
+        <v>0.5508715223121143</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4290908602630168</v>
+        <v>0.4274100756758372</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4316945148439544</v>
+        <v>0.4299988266772061</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1713891985185256</v>
+        <v>0.1697606053037788</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3537747025600311</v>
+        <v>0.3520720862572162</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1909253224359517</v>
+        <v>0.1892596039291021</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4280065847166838</v>
+        <v>0.426277511067795</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6125957222905285</v>
+        <v>0.6108042687836104</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5291473144788839</v>
+        <v>0.5302578289463966</v>
       </c>
     </row>
     <row r="28">
@@ -5024,49 +5024,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1200780472662686</v>
+        <v>0.1187144788348675</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4500448399971404</v>
+        <v>0.4485525754514441</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.5714347326538984</v>
+        <v>0.5698996630225395</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4520369578300674</v>
+        <v>0.4505359986794133</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3245094172993888</v>
+        <v>0.3230277360364084</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3986451319485838</v>
+        <v>0.3971506995123804</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2491333215817662</v>
+        <v>0.24767552781897</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2989942163266761</v>
+        <v>0.2975106253794806</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.09393653070441133</v>
+        <v>0.09250489136837814</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1846204116509256</v>
+        <v>0.1831423992552317</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.07416519992823112</v>
+        <v>0.07271046201737619</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3088005594171648</v>
+        <v>0.3072838646279621</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4596669282652144</v>
+        <v>0.4580988176991667</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4066396355555284</v>
+        <v>0.407645065521308</v>
       </c>
     </row>
     <row r="29">
@@ -5076,49 +5076,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3832</v>
+        <v>3833</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.09433801268989583</v>
+        <v>0.0931869335842137</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.3694937900307593</v>
+        <v>0.3682359778322493</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4051414783660476</v>
+        <v>0.4038653053824746</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3154323574905078</v>
+        <v>0.3141817159012845</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.285911184038909</v>
+        <v>0.2846560436178507</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3112682154801689</v>
+        <v>0.3100122638182725</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.266889245537925</v>
+        <v>0.2656424191750304</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2830206538818416</v>
+        <v>0.281758958161582</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1322228903355622</v>
+        <v>0.130998558243661</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1307305902599509</v>
+        <v>0.1294877169844426</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.01885976387251276</v>
+        <v>0.0176410247203691</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2244211325011847</v>
+        <v>0.2231489257137937</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3406832030776172</v>
+        <v>0.3393709768802324</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3182242005294711</v>
+        <v>0.3190826481556215</v>
       </c>
     </row>
     <row r="30">
@@ -5128,49 +5128,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.02269071204808881</v>
+        <v>0.02166394882581102</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2832172872697498</v>
+        <v>0.2820914247889164</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3929672817370502</v>
+        <v>0.3918048602580342</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3049592696961767</v>
+        <v>0.3038215551938279</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3489908024351323</v>
+        <v>0.3478306771807738</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2989539389943872</v>
+        <v>0.2978119836422692</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3834912376754502</v>
+        <v>0.3823252357125</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.3441979194884297</v>
+        <v>0.3430323994944402</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.271692142905323</v>
+        <v>0.2705436181760987</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1601844477712504</v>
+        <v>0.159047596262063</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.04760029122070364</v>
+        <v>0.04648800329943725</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1742003229417364</v>
+        <v>0.1730554009343663</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2862828125564292</v>
+        <v>0.2851001020337378</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2141373806075038</v>
+        <v>0.2149351097040579</v>
       </c>
     </row>
     <row r="31">
@@ -5180,49 +5180,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3884</v>
+        <v>3885</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.008486237141831054</v>
+        <v>0.007539587731422159</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2071030565588288</v>
+        <v>0.2060759621087698</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3139832883421363</v>
+        <v>0.3129211528377525</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.252868640756553</v>
+        <v>0.2518240357486192</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.2935952541323488</v>
+        <v>0.292529981471759</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2198145926641359</v>
+        <v>0.2187731269299391</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.380475483815701</v>
+        <v>0.379390706259656</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.3387614464700945</v>
+        <v>0.337678439998939</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2663193605827345</v>
+        <v>0.2652533583685184</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1506308636071054</v>
+        <v>0.1495787323668054</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.01393098146287741</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.06066434039995983</v>
+        <v>0.05963124618227766</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1182230327958962</v>
+        <v>0.1171670110099541</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.07360412222524815</v>
+        <v>0.07437444623374745</v>
       </c>
     </row>
     <row r="32">
@@ -5232,49 +5232,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.005558759097446853</v>
+        <v>-0.006426234615986459</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1573668315016263</v>
+        <v>0.1564306653785934</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1848270446815619</v>
+        <v>0.1838768744951693</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1502907767999062</v>
+        <v>0.1493511246402974</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1877367183775434</v>
+        <v>0.1867781189116684</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1415649068445077</v>
+        <v>0.1406225740989271</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3263819617908226</v>
+        <v>0.3253905455589603</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.307823747688154</v>
+        <v>0.3068288439631246</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2098692073632336</v>
+        <v>0.2088978560843273</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.09003389266628403</v>
+        <v>0.08907857980149458</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.02360567292413407</v>
+        <v>-0.02453579523007932</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.02517226349580426</v>
+        <v>0.02422977314140695</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.02884117223409532</v>
+        <v>0.02789028027405749</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03974442971338732</v>
+        <v>-0.03900816011021391</v>
       </c>
     </row>
     <row r="33">
@@ -5284,49 +5284,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3935</v>
+        <v>3936</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0111688166638757</v>
+        <v>-0.0119365420562545</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.01329670641973024</v>
+        <v>-0.01408793920101914</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1630691828343416</v>
+        <v>0.1622270743678342</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1804358641928303</v>
+        <v>0.1795908648347364</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1883001621458504</v>
+        <v>0.1874448451305781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1446557059696474</v>
+        <v>0.1438154221193599</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2767548812621783</v>
+        <v>0.275879442592057</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.229508578492613</v>
+        <v>0.2286378291681004</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1064254518227656</v>
+        <v>0.1055846197959056</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.01881271892778358</v>
+        <v>-0.0196347070751699</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1331508994533763</v>
+        <v>-0.133947287235074</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.03370671813114257</v>
+        <v>-0.0345282517626444</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.007769684660239307</v>
+        <v>-0.008604419122718809</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.04860578464188592</v>
+        <v>-0.04794953279755276</v>
       </c>
     </row>
     <row r="34">
@@ -5336,49 +5336,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3968</v>
+        <v>3969</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01918561988342304</v>
+        <v>-0.01984119376891158</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01559108190114245</v>
+        <v>0.0149061657763454</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.06156696012865126</v>
+        <v>0.06086518511411754</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07984458936759609</v>
+        <v>0.07913952163875848</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05800609295183534</v>
+        <v>0.05729938731793283</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.06746162594294702</v>
+        <v>0.06675595084921326</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07195509569216796</v>
+        <v>0.07124687926892648</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09666079997998622</v>
+        <v>0.09594012758955728</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.07473949036464944</v>
+        <v>0.07402321591299454</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1320578338180738</v>
+        <v>-0.1327331469248705</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1968107574461655</v>
+        <v>-0.1974726962482052</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1483012546250109</v>
+        <v>-0.1489753113806245</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.151298189106285</v>
+        <v>-0.1519771491931152</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.164552417424602</v>
+        <v>-0.1639591254331592</v>
       </c>
     </row>
     <row r="35">
@@ -5388,49 +5388,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01769808632095504</v>
+        <v>-0.01822946337017584</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05128473183323479</v>
+        <v>0.05071947381411235</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.01841659697301878</v>
+        <v>0.01785521240336863</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.037743010764963</v>
+        <v>0.03717787372157488</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0139017732940232</v>
+        <v>-0.01445983021115183</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.05156343623882265</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.04794453867224746</v>
+        <v>-0.04849248366502934</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.02792768920770783</v>
+        <v>-0.02848567722405448</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.0245440267569208</v>
+        <v>0.0239720608728291</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1883621887414435</v>
+        <v>-0.1888900670180647</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2295122985958074</v>
+        <v>-0.2300322841867128</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1561947874585741</v>
+        <v>-0.1567329762518952</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1631507150115965</v>
+        <v>-0.1636917552454875</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1489508198210032</v>
+        <v>-0.1484659562922133</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_recovery_7_90.xlsx
@@ -575,254 +575,254 @@
         <v>202</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.39856071495425</v>
+        <v>6.369660220470244</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.726834068889247</v>
+        <v>9.725820499115741</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.883380013465995</v>
+        <v>5.883335973636633</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.548029793490024</v>
+        <v>3.547611149562925</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.013887986644782</v>
+        <v>3.062293868242655</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.830214687177374</v>
+        <v>1.854126115132935</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.215852257008578</v>
+        <v>4.263771477529566</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.763119403731217</v>
+        <v>2.812275888129882</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.175101260297154</v>
+        <v>5.248241273115973</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.800254113485849</v>
+        <v>6.899470174853704</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.587841431439678</v>
+        <v>7.687651104720274</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.09854225482272</v>
+        <v>10.22215905895691</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.187329660839595</v>
+        <v>9.33596760736156</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.941354580540725</v>
+        <v>7.113353340107388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.02269</t>
+          <t>X ≈ 0.02268</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>210</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.264427327127926</v>
+        <v>2.235511777144886</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.184125027955716</v>
+        <v>-2.185294175793629</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.103591874657688</v>
+        <v>-2.103731333920628</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5507343966642964</v>
+        <v>-0.5511914420771831</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.458920500755525</v>
+        <v>-3.410612642114167</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.739070909252327</v>
+        <v>-1.715202977460457</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.975422519424264</v>
+        <v>2.023312866735893</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8652825468014598</v>
+        <v>-0.8161662065441107</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.9755898595937396</v>
+        <v>1.048688317548908</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.07853753419176</v>
+        <v>1.17770727832216</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07598864343485445</v>
+        <v>0.0237781453641972</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04136123594966534</v>
+        <v>0.0822187281972262</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.9368137107931389</v>
+        <v>-0.7881960489816251</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.03781</t>
+          <t>X ≈ 0.0378</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.249227951827613</v>
+        <v>-3.541343326377124</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.274483549086199</v>
+        <v>-2.525458818992</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.120535066841711</v>
+        <v>-1.362494178221645</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5571142831549025</v>
+        <v>0.3228189624995252</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.605266860290889</v>
+        <v>2.433115500709214</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.902413924279543</v>
+        <v>2.705735202180854</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.7511105774422759</v>
+        <v>0.5675266217427861</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.320291653655005</v>
+        <v>1.143258174163833</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2262753872573739</v>
+        <v>0.06771749481025324</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4127639224788453</v>
+        <v>0.2855744870607566</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.307883038253955</v>
+        <v>-0.4372526026890498</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7910363454616345</v>
+        <v>-0.8993763805267747</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6927060133826473</v>
+        <v>-0.7733919299649941</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4664328303249476</v>
+        <v>-0.5238166268894275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.05293</t>
+          <t>X ≈ 0.05292</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.97254448963362</v>
+        <v>-1.75400046761451</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.565624767619575</v>
+        <v>-1.329323314748223</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.970309922614582</v>
+        <v>-3.72283347685709</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.848684696234749</v>
+        <v>-4.596400030605395</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.365560997553658</v>
+        <v>-2.079582073212926</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.090602389918296</v>
+        <v>-4.813809087211844</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.66013327643234</v>
+        <v>-2.371888372837553</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.133571890093691</v>
+        <v>-3.83892922147696</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.195287468711989</v>
+        <v>-3.876588634466287</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.045162671021231</v>
+        <v>-4.70030140760062</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.737060035945333</v>
+        <v>-3.39907462018742</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.713116606642117</v>
+        <v>-4.346142067291161</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.629471471445271</v>
+        <v>-4.239875181502171</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.414881043021751</v>
+        <v>-4.996701886521031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.06805</t>
+          <t>X ≈ 0.06804</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>168</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4845521736899556</v>
+        <v>0.4557485699037613</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5249513689472778</v>
+        <v>-0.5260727480138314</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.101875592462569</v>
+        <v>-2.102017903493717</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.158704897625562</v>
+        <v>-3.159200674205621</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.101382635933277</v>
+        <v>-3.053202925693746</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.159167426714788</v>
+        <v>0.1830182043179036</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6664891414450835</v>
+        <v>0.7143019761430054</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.35779978024852</v>
+        <v>4.406915229236674</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.893714795138742</v>
+        <v>4.966770498128241</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.236297103065688</v>
+        <v>5.335405888138808</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.657930942575454</v>
+        <v>2.75763607621731</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.288611730106837</v>
+        <v>3.412140100620896</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.680950408232441</v>
+        <v>1.829532808801893</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.908351280210852</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="11">
@@ -835,98 +835,98 @@
         <v>218</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2600359424997336</v>
+        <v>0.2313116758356557</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02785488733164243</v>
+        <v>0.02676938793426586</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.363302695468029</v>
+        <v>-0.36339362976058</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.99290364742933</v>
+        <v>-7.993543331606709</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.594299207163864</v>
+        <v>-2.546186217496576</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.670766790645409</v>
+        <v>-3.647017115390632</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.759138806839154</v>
+        <v>-3.711442508748121</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.140347065341707</v>
+        <v>-5.091399349234706</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-6.575311020260393</v>
+        <v>-6.502439404652577</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.715137085275458</v>
+        <v>-9.616228821529681</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.090251049335329</v>
+        <v>-7.99066995317267</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-8.059446690401536</v>
+        <v>-7.936009945239832</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.565446797147573</v>
+        <v>-7.416909502203119</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.966266456792695</v>
+        <v>-5.794267697225706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.09832</t>
+          <t>X ≈ 0.09827</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>141</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.91920867629613</v>
+        <v>4.890785565934095</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.322938977470493</v>
+        <v>3.322011408223034</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.164157026407821</v>
+        <v>7.164352923492096</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.069714578588055</v>
+        <v>3.069367295357736</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.123582837509211</v>
+        <v>1.171712362894951</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.244268438304744</v>
+        <v>4.268172888160457</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.45297560502236</v>
+        <v>3.500768323613542</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8700703877016096</v>
+        <v>0.9190667603292155</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.22577511722951</v>
+        <v>2.298702108650744</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.087714530174132</v>
+        <v>2.186673929314317</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.010327158337574</v>
+        <v>4.109951836660422</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.630149182609408</v>
+        <v>2.753598070385834</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.047746205163314</v>
+        <v>5.1962918464315</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.149486031983791</v>
+        <v>3.321484791550375</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>169</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.294652346689752</v>
+        <v>-6.323449912298251</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.657270933636958</v>
+        <v>-9.658725268653612</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.23035524872766</v>
+        <v>-11.230829720988</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.806729466497522</v>
+        <v>-5.807374527023939</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.756895216249198</v>
+        <v>-5.709074734919511</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.410519553591321</v>
+        <v>-8.386995789984844</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-11.44882788652595</v>
+        <v>-11.40146211810102</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-7.201801299468023</v>
+        <v>-7.153031761720854</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6.675511979811276</v>
+        <v>-6.60280889148671</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.525945381043051</v>
+        <v>-7.42720001144923</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.370405311497656</v>
+        <v>-5.270934180058681</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.747766422202147</v>
+        <v>-4.624416319125437</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.212821990138949</v>
+        <v>-2.064327304060718</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2119643016434694</v>
+        <v>-0.03996554207687097</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>143</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.127888141203314</v>
+        <v>-2.156397785162177</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.334101424080892</v>
+        <v>-2.335278649358742</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6436359622196122</v>
+        <v>-0.643716884448601</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.983798504838106</v>
+        <v>-3.984431130153482</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.912083051957481</v>
+        <v>-5.864454124647359</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.925566349262525</v>
+        <v>-4.902047952930353</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.407754821769323</v>
+        <v>-6.360409917209964</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.483427551135314</v>
+        <v>-5.434733856725501</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9.031709355387761</v>
+        <v>-8.959195560292898</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.606642629435179</v>
+        <v>-3.507965715568609</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3754470769665161</v>
+        <v>0.4749005199441427</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.684917852640787</v>
+        <v>-1.561614571273473</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.105302818432286</v>
+        <v>-1.956847423254317</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>132</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.475746945082527</v>
+        <v>-5.504373231325886</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.061143666572555</v>
+        <v>-1.062247981274687</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0495800019823065</v>
+        <v>0.04956081445426008</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.069933699255522</v>
+        <v>-2.070521269994288</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.110945136875408</v>
+        <v>-4.063453501465318</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.846225406019528</v>
+        <v>-9.823049358927072</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.432626500677955</v>
+        <v>-8.385527976686149</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.149440058691695</v>
+        <v>-8.100969870415327</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11.98814613103733</v>
+        <v>-11.91590065478494</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.57831381327257</v>
+        <v>-10.47993622586562</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-13.81352154592436</v>
+        <v>-13.71439448939783</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.27564637831536</v>
+        <v>-12.1525411093164</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-14.21777734550759</v>
+        <v>-14.06943684331505</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.24316387130457</v>
+        <v>-13.07116511173791</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.891260048183085</v>
+        <v>-4.588367208996637</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.486435740853032</v>
+        <v>-6.156318747837325</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.497688180706895</v>
+        <v>-5.156390255659147</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.575143571355575</v>
+        <v>1.965629336093762</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.821108378050155</v>
+        <v>4.27956398122793</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.509791670788445</v>
+        <v>5.954416431283235</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.339172650401359</v>
+        <v>3.092756379442562</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7884288983986067</v>
+        <v>0.5282778584084795</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.731820591343876</v>
+        <v>0.4951957599750472</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1164335673189854</v>
+        <v>-0.3272920302195317</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.413128959679028</v>
+        <v>-2.63823969847099</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2868521611286994</v>
+        <v>-0.4734957496060019</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.485512384610345</v>
+        <v>3.353406086569997</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.414178786038093</v>
+        <v>4.310396988134123</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.86317636352809</v>
+        <v>-5.344397081869324</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.533402336286457</v>
+        <v>-5.00655867573672</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.85458062713974</v>
+        <v>-7.308735205404503</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.913745514315131</v>
+        <v>-2.414497304310807</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.448867981752478</v>
+        <v>-2.902280762248232</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.084266049202689</v>
+        <v>-4.543498281361074</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.210651160377651</v>
+        <v>-2.699550780721339</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.6771499297056</v>
+        <v>-3.164343652648725</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.736721184189562</v>
+        <v>-3.199794197729432</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-5.556002712605768</v>
+        <v>-4.983403639773591</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-8.668767696291951</v>
+        <v>-8.067068225254374</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-11.55100860635009</v>
+        <v>-10.89695474640116</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-14.8914246813324</v>
+        <v>-14.18360286588602</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-15.64828302399654</v>
+        <v>-14.90682944740247</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.023330358881651</v>
+        <v>2.779478892387921</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.495039954447606</v>
+        <v>4.226900828169214</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.13007556720558</v>
+        <v>5.349587336717676</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.284917243957331</v>
+        <v>3.214837481733902</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7.37290594742889</v>
+        <v>5.758433231190018</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.31524467416714</v>
+        <v>5.278747909973454</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.077591213661229</v>
+        <v>3.706557163961818</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>7.645446655300958</v>
+        <v>4.762672606084571</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7906228235368857</v>
+        <v>-2.115879162092455</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4123434141027005</v>
+        <v>-3.705499833216862</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.419076460671846</v>
+        <v>-4.680334479480031</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.193053353890186</v>
+        <v>-5.385795539589843</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.616212068548521</v>
+        <v>-5.782773077013815</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.586272375703494</v>
+        <v>-4.344586346991122</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5022858687923275</v>
+        <v>-0.9180169354327745</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.201012266733542</v>
+        <v>3.357639883929131</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.813153324374866</v>
+        <v>0.9888645162486753</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.942440076208442</v>
+        <v>1.768384669537838</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.911688022251901</v>
+        <v>-4.670570554109055</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.95623832130876</v>
+        <v>-0.4316847270192028</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.689609531473934</v>
+        <v>-5.103007520851449</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.507391729858384</v>
+        <v>-0.5936797659707906</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4184577261903186</v>
+        <v>1.000250557767451</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.552524464306764</v>
+        <v>3.844575157269432</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.397910088311001</v>
+        <v>2.674822670005284</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.432325457098152</v>
+        <v>2.45630338480872</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6817624600714396</v>
+        <v>0.4516142285345026</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2416846135439883</v>
+        <v>0.03840743492072818</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.163381204488779</v>
+        <v>1.55234710145178</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.59232567978124</v>
+        <v>2.008505316127831</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.270086937115224</v>
+        <v>4.666372744694257</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.347844722792736</v>
+        <v>3.788476656281915</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.480047364865179</v>
+        <v>-2.798356060475115</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.161071952741537</v>
+        <v>-2.530138610560513</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.166049209089145</v>
+        <v>-1.573038078705395</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.663983828298363</v>
+        <v>-2.03887083908868</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.380496764794877</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.639688928616479</v>
+        <v>-2.899672029040516</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.974526415601638</v>
+        <v>-5.144628803107217</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.32947111762526</v>
+        <v>-5.086462065742325</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.238910543996035</v>
+        <v>-7.522436318836768</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.383315386456147</v>
+        <v>-7.2733914568214</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>94</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.672405392236477</v>
+        <v>-5.193187687388253</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5.482365961508201</v>
+        <v>5.396695452685286</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.89610521505103</v>
+        <v>1.322234408080313</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.090160145873448</v>
+        <v>2.514074576728277</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.615700380011788</v>
+        <v>4.135418491841165</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.785414835178784</v>
+        <v>2.295063664499779</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.956023624848797</v>
+        <v>7.067865091073152</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.361295406594024</v>
+        <v>3.410542968987684</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.236483462837157</v>
+        <v>2.309740572616782</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.578054028209422</v>
+        <v>4.677401353503996</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.37335286994923</v>
+        <v>4.473260905967905</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.471560809538587</v>
+        <v>5.595257430566832</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.987580168991144</v>
+        <v>4.136269716768972</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.085656244749643</v>
+        <v>2.257655004316248</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.460507867268987</v>
+        <v>-0.02316964187226489</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.112510286863426</v>
+        <v>-3.617622965108559</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6151673079733015</v>
+        <v>2.027898383735057</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.315832038234241</v>
+        <v>-1.353027745363292</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.288735551527203</v>
+        <v>4.197518301354698</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.606517744427649</v>
+        <v>5.02235311668386</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.501399221896122</v>
+        <v>3.951596017357275</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.054738741374635</v>
+        <v>4.495864267074879</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.952940258321242</v>
+        <v>2.438689637736125</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>0.6047600468201253</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.918728466996555</v>
+        <v>2.420821619486063</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.953106619351878</v>
+        <v>2.478988356850955</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.553363929303778</v>
+        <v>3.093931440388133</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.758691416265002</v>
+        <v>2.332875292302496</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>58</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.415635693603484</v>
+        <v>5.218679488798749</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-3.261049320494934</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.038597646284259</v>
+        <v>-0.2005455715469395</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.264041290407462</v>
+        <v>5.083854637189511</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.725751737311853</v>
+        <v>3.774297657077625</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.023125766946855</v>
+        <v>4.047083175896468</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.938415407680687</v>
+        <v>3.986427086671007</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.149342891278273</v>
+        <v>-5.100095328884557</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.410364607371463</v>
+        <v>3.483621717151159</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.836307880006828</v>
+        <v>0.9356552053014013</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.528158445884664</v>
+        <v>7.628066481903339</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.390122805136443</v>
+        <v>2.513819426164687</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.969971951823119</v>
+        <v>2.118661499600947</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4715696710151818</v>
+        <v>0.6435684305818441</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>67</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2421100603851016</v>
+        <v>-0.2713058547377329</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.131778473416659</v>
+        <v>1.130591686972004</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.214619028960207</v>
+        <v>5.214465638955886</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8672322322501955</v>
+        <v>0.8667377398721925</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.806554619452875</v>
+        <v>4.855100539218647</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.103928649087962</v>
+        <v>5.127886058037575</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.034143662956211</v>
+        <v>2.082155341946532</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.059612332602228</v>
+        <v>3.108859894995945</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.4911674895122</v>
+        <v>4.564424599291897</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.626323320048179</v>
+        <v>6.725670645342753</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.914159475220742</v>
+        <v>8.014067511239418</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.45600031414331</v>
+        <v>6.579696935171555</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.543312147396982</v>
+        <v>4.69200169517481</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.261585111056355</v>
+        <v>6.433583870623018</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>56</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.247919224996643</v>
+        <v>2.296465144762415</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.331007540346008</v>
+        <v>4.354964949295621</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6748686096512699</v>
+        <v>0.7228802886415906</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.350657108721627</v>
+        <v>7.399904671115344</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>10.01118472729752</v>
+        <v>10.11053205259209</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.235054997608799</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>16.98371886424983</v>
+        <v>17.10741548527808</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14.77785372522214</v>
+        <v>14.92654327299997</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15.00358937544868</v>
+        <v>15.17558813501534</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>37</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.664654633158577</v>
+        <v>2.663467846713921</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.97258595110624</v>
+        <v>4.972432561101918</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.400108391991822</v>
+        <v>2.399613899613819</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.267224244301531</v>
+        <v>7.315770164067303</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5435098341714877</v>
+        <v>-0.5195524252218746</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.736328301545761</v>
+        <v>-8.68831662255544</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-11.90609964803513</v>
+        <v>-11.85685208564141</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-17.37248720996331</v>
+        <v>-17.29923010018361</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.411595195482285</v>
+        <v>-7.312247870187711</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.210890948337145</v>
+        <v>-2.11098291231847</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-7.581918201387225</v>
+        <v>-7.45822158035898</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1060390534074713</v>
+        <v>0.2547286011852989</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.370927999068698</v>
+        <v>-2.198929239502036</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>45</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.592027141645467</v>
+        <v>-3.621222935998098</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.203213234709295</v>
+        <v>-5.204400021153951</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.375762397242113</v>
+        <v>-3.375915787246434</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.689981698098194</v>
+        <v>-7.690476190476197</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-14.89493791786055</v>
+        <v>-14.84639199809478</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-12.37534166600324</v>
+        <v>-12.35138425705363</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-14.68227424749163</v>
+        <v>-14.63426256850131</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.70489844683393</v>
+        <v>-10.65565088444021</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.321436158912263</v>
+        <v>-6.248179049132567</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-13.83802162190879</v>
+        <v>-13.73867429661421</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.598278335724537</v>
+        <v>-9.498370299705861</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.563900183369213</v>
+        <v>-9.440203562340969</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-12.20627325890484</v>
+        <v>-12.05758371112702</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-9.75831538645609</v>
+        <v>-9.586316626889428</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.603723048078265</v>
+        <v>-0.724397539172692</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.969295106054325</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-10.62722438554621</v>
+        <v>-9.844169755500396</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.742613277045564</v>
+        <v>-7.928571428571431</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.263358970492177</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.47475687068156</v>
+        <v>-4.573606479275902</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.458076629701402</v>
+        <v>2.508594574355783</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7633779789976671</v>
+        <v>0.2570475282582052</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.684411794304118</v>
+        <v>2.005789204835743</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.428664896762633</v>
+        <v>-2.389467947407809</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.633366055022726</v>
+        <v>-4.379322680658234</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.353373867579791</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.527910685805473</v>
+        <v>-8.287742441285744</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.54778907066661</v>
+        <v>-6.252983293556035</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-9.147582697200924</v>
+        <v>-10.57462795391924</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-10.7587687902649</v>
+        <v>-12.15780503907514</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-2.874123672551093</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.023315031431572</v>
+        <v>-2.744239631336455</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.438395415472833</v>
+        <v>6.443930582550337</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.26423055489218</v>
+        <v>-2.960703253469255</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15.31772575250822</v>
+        <v>13.1076729153697</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.183990442054956</v>
+        <v>6.190227251760504</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>18.12300828553218</v>
+        <v>19.05648044907523</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.939756155869091</v>
+        <v>2.103619610195729</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.735054997608707</v>
+        <v>5.125285614272634</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.230566850035778</v>
+        <v>-4.493967003201185</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.650717703349187</v>
+        <v>-4.889124929765011</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-13.09164871978942</v>
+        <v>-11.09169297097554</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>22</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.18301121450721</v>
+        <v>-13.18419800095187</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-13.57778259926231</v>
+        <v>-13.57793598926663</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.902102910219341</v>
+        <v>-8.902597402597344</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.440392463315035</v>
+        <v>-9.391846543549264</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-13.68847297913462</v>
+        <v>-13.66451557018501</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1368197020370232</v>
+        <v>-0.08880802304670254</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.81039954784575</v>
+        <v>-10.71049151182707</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-19.86693048639945</v>
+        <v>-19.74323386537121</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-29.37799043062195</v>
+        <v>-29.22930088284412</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-24.60680023494094</v>
+        <v>-24.43480147537428</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.637556669052728</v>
+        <v>-11.23614605289998</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-22.6686916901714</v>
+        <v>-21.15369356502421</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-17.99301200112856</v>
+        <v>-16.26190476190477</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-18.53130155422426</v>
+        <v>-16.75115390285669</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-13.68847297913455</v>
+        <v>-11.71646362213306</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-9.227728792946181</v>
+        <v>-7.0152149494537</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-9.755779593255696</v>
+        <v>-7.518020318973839</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-10.60569838958556</v>
+        <v>-8.341848899788822</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>0.9778201764845491</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.230566850035942</v>
+        <v>-3.725917848055381</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-15.74162679425844</v>
+        <v>-13.64488529842867</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-20.06134568948639</v>
+        <v>-18.157745198318</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.7567780994998685</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-23.05761936497749</v>
+        <v>-20.75995557670951</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.762735577318736</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.264041290407654</v>
+        <v>2.309523809523846</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.277475875242942</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5748499048779792</v>
+        <v>-1.240273145942474</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.406412178526118</v>
+        <v>-7.967595901834649</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.32175668438182</v>
+        <v>-11.76676199555132</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-13.83101470297356</v>
+        <v>-15.13706793802145</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-14.68093349930342</v>
+        <v>-15.96089651883644</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-14.88563465756361</v>
+        <v>-16.16503696637248</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.954704781070411</v>
+        <v>-9.440203562340969</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.926579772314803</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.252568260019309</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9657645153827943</v>
+        <v>-0.9949603097354256</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.483655452159354</v>
+        <v>3.482468665714698</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.06263108411077</v>
+        <v>-12.06278447411509</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.93240594052244</v>
+        <v>-11.93290043290044</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-15.50099852392116</v>
+        <v>-15.45245260415539</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.143018433680055</v>
+        <v>-9.119061024730442</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-24.37924394446133</v>
+        <v>-24.33123226547101</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-15.755403497339</v>
+        <v>-15.70615593494529</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.695173532649676</v>
+        <v>-3.62191642286998</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-13.63600141988863</v>
+        <v>-13.53665409459406</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.780096517542759</v>
+        <v>-7.680188481524084</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.80632442579346</v>
+        <v>-13.68262780476521</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-17.25677830940993</v>
+        <v>-17.1080887616321</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-14.00073962888033</v>
+        <v>-13.82874086931367</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.431</t>
+          <t>X ≈ 0.4309</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>38</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1506629168340297</v>
+        <v>0.1214671224813983</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.802634718507115</v>
+        <v>3.801447932062459</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.486873508353234</v>
+        <v>-4.487026898357556</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.356648364764915</v>
+        <v>-4.357142857142918</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.526516865228977</v>
+        <v>-7.477970945463206</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-12.49230073033069</v>
+        <v>-12.46834332138108</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-12.5770110895969</v>
+        <v>-12.52899941060658</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-13.04407973338364</v>
+        <v>-12.99483217098992</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.210325047801092</v>
+        <v>-5.137067938021396</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.060243844130973</v>
+        <v>-5.9608965188364</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-3.633366055022741</v>
+        <v>-3.533458019004065</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.9674089552989997</v>
+        <v>-0.8437123342707551</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.38755980861238</v>
+        <v>-1.238870260834553</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.46975478898252</v>
+        <v>1.641753548549183</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3159</v>
+        <v>3170</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.7469942146453263</v>
+        <v>-0.735056845307966</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.7335401557646861</v>
+        <v>-0.7306239194708724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.048387703936818</v>
+        <v>-1.044713160539246</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.216856632357157</v>
+        <v>-1.212488769092545</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9176651905878259</v>
+        <v>-0.9300661094505571</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.076881854755307</v>
+        <v>-1.08084373541179</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.176272984067758</v>
+        <v>-1.18761478757591</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.342075908655936</v>
+        <v>-1.353243943494228</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.10160191252934</v>
+        <v>-1.121319906525393</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.175640619344406</v>
+        <v>-1.203492612094152</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.8886009163696968</v>
+        <v>-0.9176370294043608</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.026517498564829</v>
+        <v>-1.062734037330458</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.27097086790625</v>
+        <v>-1.31439018647653</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.280949131312049</v>
+        <v>-1.33184764686839</v>
       </c>
     </row>
     <row r="7">
@@ -2266,361 +2266,361 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2957</v>
+        <v>2968</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.2351247847431</v>
+        <v>-1.21859890975783</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.448114248892892</v>
+        <v>-1.442282198633436</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.52191393962007</v>
+        <v>-1.516231329374662</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.542357835610829</v>
+        <v>-1.536457833637151</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.1862393339091</v>
+        <v>-1.201783331652052</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.27547282583086</v>
+        <v>-1.280595726587677</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.544622425629278</v>
+        <v>-1.558632316400477</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.622511976664804</v>
+        <v>-1.636746304002344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.530379065356847</v>
+        <v>-1.554827776568374</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.720493759700069</v>
+        <v>-1.754974580747607</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.467647705093903</v>
+        <v>-1.503306909152734</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.78649790782567</v>
+        <v>-1.830775952913356</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.985403301726564</v>
+        <v>-2.03924607406254</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.84263507983902</v>
+        <v>-1.906622107572268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.03025</t>
+          <t>X &gt; 0.03024</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2747</v>
+        <v>2758</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.502655160969134</v>
+        <v>-1.481602261552446</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.391848408484009</v>
+        <v>-1.385707682606011</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.477446387250971</v>
+        <v>-1.471497826490449</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.618164505497539</v>
+        <v>-1.611478117258471</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.012499601459972</v>
+        <v>-1.033598358774213</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.240032127789895</v>
+        <v>-1.247503803932396</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.813719418152488</v>
+        <v>-1.831369259278894</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.680399919974342</v>
+        <v>-1.699227022082916</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.721952954777898</v>
+        <v>-1.753065042617905</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.93447139774787</v>
+        <v>-1.978275229915361</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.574035911482113</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.919908428791793</v>
+        <v>-1.976435446398938</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.065564864921335</v>
+        <v>-2.134503690185454</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.747151692729602</v>
+        <v>-1.829488007116645</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.04537</t>
+          <t>X &gt; 0.04536</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2554</v>
+        <v>2566</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.370670607861967</v>
+        <v>-1.327482898946698</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.325149668415008</v>
+        <v>-1.300426225791476</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.504417368002343</v>
+        <v>-1.479653984116176</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.782545400646292</v>
+        <v>-1.756211180124225</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.285886025546858</v>
+        <v>-1.292993939842347</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.553067401106027</v>
+        <v>-1.543303448972821</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.007537816410029</v>
+        <v>-2.010865755442623</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.907155391278366</v>
+        <v>-1.911914924530066</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.869176161517444</v>
+        <v>-1.889304421879878</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.111846658829997</v>
+        <v>-2.147666946851999</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.66971621866027</v>
+        <v>-1.708049811837682</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.005214737359815</v>
+        <v>-2.05702599224751</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.169308701392339</v>
+        <v>-2.236348373724951</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.8439327187453</v>
+        <v>-1.927184384748607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.06049</t>
+          <t>X &gt; 0.06048</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2356</v>
+        <v>2367</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.320088677220724</v>
+        <v>-1.291624429929008</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.30493996143602</v>
+        <v>-1.297996770488396</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.297181915619809</v>
+        <v>-1.291063904244844</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.524864763750486</v>
+        <v>-1.517428932027165</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.195149334351044</v>
+        <v>-1.226863378566158</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.255770318005503</v>
+        <v>-1.268343321381117</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.95269320644212</v>
+        <v>-1.9805136215763</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.720045685520539</v>
+        <v>-1.749905695509177</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.673688029588533</v>
+        <v>-1.722228140382327</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.865328589893721</v>
+        <v>-1.933060162868486</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.495975099890138</v>
+        <v>-1.565880848229071</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.77764064138448</v>
+        <v>-1.864573901443258</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.962554784384494</v>
+        <v>-2.067906533949838</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.543827553971646</v>
+        <v>-1.669121865588195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.07561</t>
+          <t>X &gt; 0.0756</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2188</v>
+        <v>2199</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.458653422628849</v>
+        <v>-1.425120866478302</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.364829396325462</v>
+        <v>-1.356970502082632</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.235395563832988</v>
+        <v>-1.22910834632134</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.399414515811266</v>
+        <v>-1.392000258682017</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.048784071706706</v>
+        <v>-1.087334027080288</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.364412704254605</v>
+        <v>-1.379224965909287</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.153800443391404</v>
+        <v>-2.186393121538487</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.186717549436985</v>
+        <v>-2.220276734780349</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.177949306807072</v>
+        <v>-2.233256685752849</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.410608807634659</v>
+        <v>-2.488359069903154</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.814922181761347</v>
+        <v>-1.896190463193598</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.166639909396608</v>
+        <v>-2.267706212651433</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.242312038662213</v>
+        <v>-2.365664519207819</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.808894301751643</v>
+        <v>-1.955575380868503</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.09074</t>
+          <t>X &gt; 0.09073</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.648843413287757</v>
+        <v>-1.607403700513863</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.518943697765692</v>
+        <v>-1.509244755501946</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.331901272108894</v>
+        <v>-1.324376295947907</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6697796778961731</v>
+        <v>-0.6655306019946892</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8777575237221029</v>
+        <v>-0.9267940081450305</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.109191795202214</v>
+        <v>-1.129664800040054</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.976153863070792</v>
+        <v>-2.018568403511381</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.859869207067838</v>
+        <v>-1.904322807495625</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.691337706028996</v>
+        <v>-1.763452630871406</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.602290450007402</v>
+        <v>-1.703969566695378</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.120494926364849</v>
+        <v>-1.225520837340262</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.514542509265091</v>
+        <v>-1.64393528195771</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.653254486707993</v>
+        <v>-1.809798084935743</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.348839921143053</v>
+        <v>-1.533144828134589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.1059</t>
+          <t>X &gt; 0.1058</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1829</v>
+        <v>1840</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.155183131511549</v>
+        <v>-2.105362769301443</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.892210760208719</v>
+        <v>-1.879466015874364</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.98687350835322</v>
+        <v>-1.974871306785424</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9580621766191229</v>
+        <v>-0.9517374517374577</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.03204346737089</v>
+        <v>-1.087603463751897</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.521897040103525</v>
+        <v>-1.543303448972821</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.394692548145223</v>
+        <v>-2.441517576622587</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.070323817708896</v>
+        <v>-2.120680377638713</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.993313052163195</v>
+        <v>-2.074737314715222</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.886757755751304</v>
+        <v>-2.002111269378737</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.516036705447966</v>
+        <v>-1.63438042811967</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.8340622077639</v>
+        <v>-1.980920174718811</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.169843386409397</v>
+        <v>-2.346677802502469</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.695621746944511</v>
+        <v>-1.905157206599576</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1660</v>
+        <v>1671</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.733755241532563</v>
+        <v>-1.678757905647075</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.101671501588612</v>
+        <v>-1.092694732978075</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.045820246833173</v>
+        <v>-1.038751036288581</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4644327959025816</v>
+        <v>-0.4606526727288269</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5510194037802592</v>
+        <v>-0.6202015219043062</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8205854709592799</v>
+        <v>-0.8511526377034926</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.472916119117308</v>
+        <v>-1.535335274103225</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.547902315047878</v>
+        <v>-1.611723235861405</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.51663135410746</v>
+        <v>-1.616781541840069</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.312647690284855</v>
+        <v>-1.453433832269269</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.123634118446518</v>
+        <v>-1.26659013244182</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.537426055812048</v>
+        <v>-1.713564789677093</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.165467853861024</v>
+        <v>-2.375233897198257</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.846668800110706</v>
+        <v>-2.093797177457944</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1517</v>
+        <v>1528</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.696602305044159</v>
+        <v>-1.634057314828581</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9854964990069419</v>
+        <v>-0.9764057931597208</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.083732147096676</v>
+        <v>-1.075720855472554</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1326797989495319</v>
+        <v>-0.1308749767787489</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.04565875665478814</v>
+        <v>-0.1294108660193132</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.433629461995956</v>
+        <v>-0.4720439792758526</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.00773356507694</v>
+        <v>-1.08377396915278</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.176920041639505</v>
+        <v>-1.253941482730809</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8082225510863026</v>
+        <v>-0.9296315388042302</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.096404264906816</v>
+        <v>-1.26115761544218</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.264945002391194</v>
+        <v>-1.429569951349663</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.523522742070114</v>
+        <v>-1.727785261687373</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.171139310727412</v>
+        <v>-2.414389175846154</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.843571374151104</v>
+        <v>-2.12994664434143</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1385</v>
+        <v>1396</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.336423898917758</v>
+        <v>-1.26809621097641</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9782868050584526</v>
+        <v>-0.9682889100428369</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.191744568525138</v>
+        <v>-1.182122847184836</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.0519537857727741</v>
+        <v>0.05252997358260103</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3417909200160594</v>
+        <v>0.2425759734354642</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4634554944019555</v>
+        <v>0.4121485064791344</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3000903394456529</v>
+        <v>-0.3933502377814335</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5123910580648499</v>
+        <v>-0.6065147297405815</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2573008514794211</v>
+        <v>0.1091847386380707</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1927132465788119</v>
+        <v>-0.3894679474078657</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.06897958452376685</v>
+        <v>-0.2679676311330681</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.498771608507397</v>
+        <v>-0.7420633620548429</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.023012075643663</v>
+        <v>-1.312335958005249</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7571120170216687</v>
+        <v>-1.095390170346924</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.9271311699765832</v>
+        <v>-0.8921165604828829</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3440957440128614</v>
+        <v>-0.380808657278223</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6959716727586454</v>
+        <v>-0.7320861868950885</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1234215277041599</v>
+        <v>-0.1641048824593199</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05880682273665627</v>
+        <v>-0.2145630194724504</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1175638882254688</v>
+        <v>-0.2154448310983597</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7191037110624947</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6621634040988909</v>
+        <v>-0.7350159638052958</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2026661310280389</v>
+        <v>0.06547376174026454</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2014958505515594</v>
+        <v>-0.3965086015073425</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2009184514240587</v>
+        <v>0.0004363828717046658</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5231713516435903</v>
+        <v>-0.7724753245490419</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.542109497395948</v>
+        <v>-1.840673573898151</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.352518285006809</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5711938083121311</v>
+        <v>-0.4894755394183719</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.03474409707948922</v>
+        <v>0.03752004004322629</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.137328362612493</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.03847783192792065</v>
+        <v>0.03940886699506763</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.157326890501821</v>
+        <v>0.02850015030901432</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2411457891938866</v>
+        <v>0.175961741794957</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4937925720989611</v>
+        <v>-0.6152478753293167</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3895175637674626</v>
+        <v>-0.5153202423794667</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5589057214296247</v>
+        <v>0.3607675598140503</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2827132862276969</v>
+        <v>0.01830625412717524</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.00300596083121</v>
+        <v>0.7300194083022333</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4740781981674473</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3349282296650813</v>
+        <v>-0.7244434466227219</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.05974939289448145</v>
+        <v>-0.5138528587734754</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.010327795240237</v>
+        <v>-0.909723852045083</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.51015904214578</v>
+        <v>-0.5010559003341015</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9049304269008189</v>
+        <v>-0.8427120295528781</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4802990026451326</v>
+        <v>-0.3688160088938375</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7241822750735025</v>
+        <v>-0.7081252016001329</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.623079099216632</v>
+        <v>-0.4800392278138617</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.296602019817449</v>
+        <v>-1.170847934354967</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.371128956047748</v>
+        <v>-1.193845328884656</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.530597425211603</v>
+        <v>0.6791588459472635</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3676266171055005</v>
+        <v>0.497029117171401</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.298905685231588</v>
+        <v>1.425560487104462</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.7999149592069941</v>
+        <v>0.8539140847178572</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.0562295143729088</v>
+        <v>-0.07415769433495001</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.126742084808285</v>
+        <v>-0.02138368609779917</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.098427551271676</v>
+        <v>-0.9082811612714252</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.327125165072836</v>
+        <v>-1.172326710730118</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.376274430012209</v>
+        <v>-1.161338824963046</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9004271666081749</v>
+        <v>-0.7406101361325241</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1714356137130864</v>
+        <v>-0.01880579119823267</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5653058237093376</v>
+        <v>-0.4884511282977186</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5348088097036126</v>
+        <v>-0.4867971307132919</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.347499573306017</v>
+        <v>-1.2982520109123</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5500436157933208</v>
+        <v>0.6233007255730172</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1846678072646526</v>
+        <v>-0.08532048197007924</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.108326887009724</v>
+        <v>1.2082349230284</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5168379942547858</v>
+        <v>0.5751574207619541</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1842050012707688</v>
+        <v>-0.1656226256175444</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1068098543916989</v>
+        <v>-0.03178513687406337</v>
       </c>
     </row>
     <row r="21">
@@ -2994,101 +2994,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.505623442758022</v>
+        <v>-1.221452031072552</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.816419418786737</v>
+        <v>-1.577159877784773</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.081151791838266</v>
+        <v>-1.903047570192165</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.43077060143586</v>
+        <v>-1.317039364258001</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2416030444281319</v>
+        <v>0.3349551521642837</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2412569961578441</v>
+        <v>-0.2285999941915478</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4560063671275216</v>
+        <v>-0.3485482827870285</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.183153034321279</v>
+        <v>-1.203991432780761</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4463719613015797</v>
+        <v>0.4473476463941282</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2466482234892737</v>
+        <v>0.2728697149297972</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.992532240781749</v>
+        <v>2.016781215445654</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.246676322916009</v>
+        <v>1.295727173589768</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6964864578990912</v>
+        <v>0.7706991171558144</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7921830964221144</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.242</t>
+          <t>X &gt; 0.2419</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9253604749787954</v>
+        <v>-0.669169262294929</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.832842864338922</v>
+        <v>-2.546897157465523</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.635021656501372</v>
+        <v>-2.35153352575076</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.060352068468561</v>
+        <v>-1.849768225874428</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2282712511938882</v>
+        <v>-0.1935116435896092</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5234898141513895</v>
+        <v>-0.5795236390391594</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-1.379824698678824</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-1.845657459062167</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1970823596062559</v>
+        <v>0.1883758489608027</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3565401404273061</v>
+        <v>-0.3395947436885081</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.660980923534723</v>
+        <v>1.675199720018007</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.658322038853008</v>
+        <v>0.6978634988030166</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2381711855395992</v>
+        <v>0.3027055722391907</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6120549839142839</v>
+        <v>0.6996794283373973</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>577</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8344688901530759</v>
+        <v>-0.7800080186586058</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.445654983216905</v>
+        <v>-2.363185103814459</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.187046818578523</v>
+        <v>-3.102943853374846</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.016960323170402</v>
+        <v>-1.934997528423132</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9954578485364607</v>
+        <v>-0.9469119287706889</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.564634945417843</v>
+        <v>-1.54067753646823</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.342586205897177</v>
+        <v>-2.294574526906857</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.982965074987206</v>
+        <v>-2.933717512593489</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2709836266572978</v>
+        <v>-0.1977265168776015</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6009717470772813</v>
+        <v>-0.5016244217827079</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.447360023605334</v>
+        <v>1.54726805962401</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2685665988376087</v>
+        <v>0.3922632198658533</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3248944797790969</v>
+        <v>-0.1762049320012693</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2474616210540219</v>
+        <v>0.4194603806206842</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>519</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.42118578005266</v>
+        <v>-1.450381574405291</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.261658963675259</v>
+        <v>-2.262845750119915</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.427143257871528</v>
+        <v>-3.427296647875849</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.718883432202233</v>
+        <v>-2.719377924580236</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.523068939055158</v>
+        <v>-1.474523019289386</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.189086046221611</v>
+        <v>-2.165128637271998</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.044509314929009</v>
+        <v>-2.996497635938688</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.740865049274518</v>
+        <v>-2.691617486880801</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6823867048339096</v>
+        <v>-0.6091295950542133</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.7615925917225255</v>
+        <v>-0.6622452664279521</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.7678102962600519</v>
+        <v>0.8677183322787272</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.03147553917414569</v>
+        <v>0.1551721602023903</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5813535414995741</v>
+        <v>-0.4326639937217465</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.222416790807884</v>
+        <v>0.3944155503745463</v>
       </c>
     </row>
     <row r="25">
@@ -3205,150 +3205,150 @@
         <v>452</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.595960278321961</v>
+        <v>-1.625156072674592</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.764668495279594</v>
+        <v>-2.765855281724249</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.708112446406318</v>
+        <v>-4.708265836410639</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.250453674499376</v>
+        <v>-3.250948166877379</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.461309599276483</v>
+        <v>-2.412763679510711</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.270130259906878</v>
+        <v>-3.246172850957265</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.797318495279242</v>
+        <v>-3.749306816288922</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.600670324906694</v>
+        <v>-3.551422762512978</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.449263100898492</v>
+        <v>-1.376005991118795</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.856704021122155</v>
+        <v>-1.757356695827582</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.2914936749575716</v>
+        <v>-0.1915856389388964</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9208323367615421</v>
+        <v>-0.7971357157332974</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.340983190074951</v>
+        <v>-1.192293642297123</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6727696637422227</v>
+        <v>-0.5007709041755604</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.3025</t>
+          <t>X &gt; 0.3024</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>396</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.9657645153828369</v>
+        <v>-0.9949603097354682</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-5.749499770979483</v>
+        <v>-5.749653160983804</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.104123112239613</v>
+        <v>-4.104617604617616</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.127261150183791</v>
+        <v>-3.07871523041802</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.34503863570022</v>
+        <v>-4.321081226750607</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.429748994966388</v>
+        <v>-4.381737315976068</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.43254727002337</v>
+        <v>-2.359290160243674</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.534991318878475</v>
+        <v>-3.435643993583902</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.214439951886149</v>
+        <v>-1.114531915867474</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.452789072258099</v>
+        <v>-3.329092451229855</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.620414673046255</v>
+        <v>-3.471725125268428</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.889628517769218</v>
+        <v>-2.717629758202555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.3176</t>
+          <t>X &gt; 0.3175</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>359</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.227434136383934</v>
+        <v>-1.256629930736565</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.788480953681749</v>
+        <v>-4.789667740126404</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.854561530637341</v>
+        <v>-6.854714920641662</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.774475662815</v>
+        <v>-4.774970155193003</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.198559087776985</v>
+        <v>-4.150013168011213</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.736839654242175</v>
+        <v>-4.712882245292562</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.985895417408067</v>
+        <v>-3.937883738417746</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.452964061194805</v>
+        <v>-4.403716498801089</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8927763012830425</v>
+        <v>-0.8195191915033462</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.13545275778003</v>
+        <v>-3.036105432485456</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.111741659772818</v>
+        <v>-1.011833623754143</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.027224231651481</v>
+        <v>-2.903527610623236</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.004478149031733</v>
+        <v>-3.855788601253906</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.943087902704924</v>
+        <v>-2.771089143138262</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>314</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.8885593426362632</v>
+        <v>-0.9177551369888945</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.729044798757414</v>
+        <v>-4.73023158520207</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.353115546569782</v>
+        <v>-7.353268936574104</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.66563855480323</v>
+        <v>-2.617092635037459</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.642149875486609</v>
+        <v>-3.618192466536996</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.452974884434312</v>
+        <v>-2.404963205443991</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.556986203380283</v>
+        <v>-3.507738640986567</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1147836465272647</v>
+        <v>-0.04152653674756834</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.601645118016357</v>
+        <v>-1.502297792721784</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.104481749201156</v>
+        <v>0.2043897852198313</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.09043946150085</v>
+        <v>-1.966742840472605</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.829061652393875</v>
+        <v>-2.680372104616048</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.966383327008103</v>
+        <v>-1.79438456744144</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7299432678884301</v>
+        <v>-0.9597242279877563</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.675759711146817</v>
+        <v>-4.868482708492451</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.626951329364893</v>
+        <v>-6.812608293706376</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.383885718850465</v>
+        <v>-3.581949058693247</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.754860096848873</v>
+        <v>-2.90840750197075</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.235696183945315</v>
+        <v>-3.410815781601428</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.320406543211483</v>
+        <v>-3.471471870826889</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.176580245363979</v>
+        <v>-4.324901530435042</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.7356168765949249</v>
+        <v>-0.4859051473237841</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.19643061455902</v>
+        <v>-1.309733728138767</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.9334985773753317</v>
+        <v>1.199304118898795</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.366753620463889</v>
+        <v>-1.068110539085154</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.786904473777298</v>
+        <v>-1.46326846564898</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.172063765185008</v>
+        <v>-0.8266267044088096</v>
       </c>
     </row>
     <row r="30">
@@ -3465,150 +3465,150 @@
         <v>227</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3825200928136638</v>
+        <v>0.3533242984610325</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.87183780641756</v>
+        <v>-3.873024592862215</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.350309631701236</v>
+        <v>-7.350463021705558</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.695855413223001</v>
+        <v>-3.696349905601004</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.234144966318695</v>
+        <v>-4.185599046552923</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.496242302322386</v>
+        <v>-3.472284893372773</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-5.783595833394713</v>
+        <v>-5.735584154404393</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-5.810135842820223</v>
+        <v>-5.760888280426506</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.227946193175598</v>
+        <v>-3.154689083395901</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.875221817699291</v>
+        <v>-1.775874492404718</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5632488302079182</v>
+        <v>0.6631568662265934</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7239589205204595</v>
+        <v>-0.6002622994922149</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.144109773833868</v>
+        <v>-0.9954202260560407</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.403211779476365</v>
+        <v>0.5752105390430273</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.3781</t>
+          <t>X &gt; 0.378</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.6898156767827217</v>
+        <v>0.6606198824300904</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.872589928476231</v>
+        <v>-2.873776714920886</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.681995459572732</v>
+        <v>-6.682148849577054</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.137136169642908</v>
+        <v>-3.137630662020911</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.675425722738602</v>
+        <v>-3.62687980297283</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.402441937005953</v>
+        <v>-2.37848452805634</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.389591320662369</v>
+        <v>-6.341579641672048</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.368855086400323</v>
+        <v>-6.319607524006607</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.503007974630414</v>
+        <v>-3.429750864850718</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.913902380716372</v>
+        <v>-1.814555055421799</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.783835485413675</v>
+        <v>1.883743521432351</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.330408759720214</v>
+        <v>1.454105380748459</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.885867662504367</v>
+        <v>2.034557210282195</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.087213068828461</v>
+        <v>3.259211828395124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.3932</t>
+          <t>X &gt; 0.3931</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.070996537771663</v>
+        <v>1.29423600119997</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.179533817587249</v>
+        <v>-1.919375866564579</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.76009755206907</v>
+        <v>-5.030505159227111</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.351183883890535</v>
+        <v>-1.639751552795033</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.889473436986229</v>
+        <v>-2.129000693746953</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.04565131991945</v>
+        <v>-1.312736914058455</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.048394466070867</v>
+        <v>-6.264697351110009</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-6.515463109857606</v>
+        <v>-6.730530111493351</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.751308654358525</v>
+        <v>-2.963154894543194</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8689870135299174</v>
+        <v>-1.069592171010349</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.205000352800056</v>
+        <v>1.987136946670958</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.239378505155379</v>
+        <v>2.045303684035851</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.005020001568745</v>
+        <v>3.824058800950283</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.87009991409036</v>
+        <v>5.703538445574338</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>154</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.415187865569543</v>
+        <v>1.385992071216911</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.752053720557662</v>
+        <v>1.750866934113006</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-5.136224157703872</v>
+        <v>-5.136377547708193</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.408596416712918</v>
+        <v>-2.409090909090921</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.297535320457953</v>
+        <v>-2.248989400692182</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.350810641472222</v>
+        <v>-1.326853232522609</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.98097554619293</v>
+        <v>-5.932963867202609</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.798693540629024</v>
+        <v>-5.749445978235308</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.731963948076789</v>
+        <v>1.831311273371362</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.423366685920492</v>
+        <v>5.523274721939167</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.159043539574519</v>
+        <v>4.282740160602764</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.686944634313051</v>
+        <v>5.835634182090878</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>7.383380342807541</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>121</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.279798702848105</v>
+        <v>1.278611916403449</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.247204086865622</v>
+        <v>-3.247357476869944</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.303409189577465</v>
+        <v>1.351955109343237</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.7743369382208201</v>
+        <v>0.7982943471704331</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.9632659830288262</v>
+        <v>-0.9152543040385055</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.083227188799029</v>
+        <v>-3.033979626405312</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1615757786451368</v>
+        <v>0.2348328884248332</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.923227230249161</v>
+        <v>6.022574555543734</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.024311195955917</v>
+        <v>9.124219231974593</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.058689348311241</v>
+        <v>9.182385969339485</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.94432361896477</v>
+        <v>12.0930131667426</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.99650555018304</v>
+        <v>13.1685043097497</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.4386</t>
+          <t>X &gt; 0.4385</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.940770716453599</v>
+        <v>2.911574922100968</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1247653462813361</v>
+        <v>0.1235785598366803</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.679644592690572</v>
+        <v>-2.679797982694893</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.269857659331535</v>
+        <v>2.269363166953532</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.346025937561137</v>
+        <v>5.394571857326909</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.848219244304651</v>
+        <v>6.872176653254265</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.353870330821621</v>
+        <v>4.401882009811942</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.477163132818021</v>
+        <v>1.526410695211737</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2.621000253403665</v>
+        <v>2.694257363183361</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>11.40963567394128</v>
+        <v>11.50898299923585</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.81939234700639</v>
+        <v>14.91930038302506</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.64895122225328</v>
+        <v>13.77264784328153</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>18.0480774773736</v>
+        <v>18.19676702515142</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.27381312760013</v>
+        <v>18.44581188716679</v>
       </c>
     </row>
   </sheetData>
@@ -3935,358 +3935,358 @@
         <v>1133</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.388457314567148</v>
+        <v>3.359261520214517</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.983802554248243</v>
+        <v>3.982615767803587</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.85381492942259</v>
+        <v>3.853661539418269</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.337085086250148</v>
+        <v>4.336590593872145</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.445750519915258</v>
+        <v>3.49429643968103</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.654863296240549</v>
+        <v>3.678820705190162</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.187981710142964</v>
+        <v>4.235993389133284</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.250480586215012</v>
+        <v>4.299728148608729</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.277759683002031</v>
+        <v>4.351016792781728</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.66349843300933</v>
+        <v>4.762845758303904</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.105752261509949</v>
+        <v>4.205660297528624</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.111004200273044</v>
+        <v>5.234700821301288</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.926510893296786</v>
+        <v>6.075200441074614</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.622679023664531</v>
+        <v>5.794677783231194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.03025</t>
+          <t>X &lt; 0.03024</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1343</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.215286501111216</v>
+        <v>3.186090706758584</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.018843520482235</v>
+        <v>3.01765673403758</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.921912790976641</v>
+        <v>2.92175940097232</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.573359081251525</v>
+        <v>3.572864588873522</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.364928053844586</v>
+        <v>2.413473973610358</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.811222411104396</v>
+        <v>2.835179820054009</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.843414509023624</v>
+        <v>3.891426188013945</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.450806029049247</v>
+        <v>3.500053591442963</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.762124691588284</v>
+        <v>3.83538180136798</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.103568516256182</v>
+        <v>4.202915841550755</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.452106375121829</v>
+        <v>3.552014411140505</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.305546329413112</v>
+        <v>4.429242950441356</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.853377605660391</v>
+        <v>5.002067153438219</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.260051453950965</v>
+        <v>4.432050213517627</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.04537</t>
+          <t>X &lt; 0.04536</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.401896469465647</v>
+        <v>2.343308370552755</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.353210376401819</v>
+        <v>2.323649200706342</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.414168158313444</v>
+        <v>2.385937271023572</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.195434968568478</v>
+        <v>3.167287110283844</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.396728748806112</v>
+        <v>2.417451650113684</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.824311111774534</v>
+        <v>2.820530328541736</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.455746585841702</v>
+        <v>3.476486617166444</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.20609359619678</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.318320785532187</v>
+        <v>3.364560726473655</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.640276989202327</v>
+        <v>3.713370582140762</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.979846664275463</v>
+        <v>3.053204075972751</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.665266483297458</v>
+        <v>3.762836611383243</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.156573963317378</v>
+        <v>4.279730802083257</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.666163780210582</v>
+        <v>3.81216328624847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.06049</t>
+          <t>X &lt; 0.06048</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1734</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.90201361191086</v>
+        <v>1.872817817558229</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.905591071326846</v>
+        <v>1.90440428488219</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.683830067194641</v>
+        <v>1.68367667719032</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.275416225777242</v>
+        <v>2.274921733399239</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.852466926430111</v>
+        <v>1.901012846195883</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.919160448568078</v>
+        <v>1.943117857517692</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.757172119290374</v>
+        <v>2.805183798280694</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.347773602377913</v>
+        <v>2.39702116477163</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.459801826477978</v>
+        <v>2.533058936257675</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.647945313885138</v>
+        <v>2.747292639179712</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.212563648127826</v>
+        <v>2.312471684146502</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.708302815477381</v>
+        <v>2.831999436505626</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.153203865278165</v>
+        <v>3.301893413055993</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.629227866139068</v>
+        <v>2.801226625705731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.07561</t>
+          <t>X &lt; 0.0756</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1902</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.777759048329997</v>
+        <v>1.748563253977366</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.69128378597069</v>
+        <v>1.690096999526034</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.349088636757187</v>
+        <v>1.348935246752866</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.794771193594755</v>
+        <v>1.794276701216752</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.414210347123678</v>
+        <v>1.46275626688945</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.764160612300302</v>
+        <v>1.788118021249915</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.573246257240228</v>
+        <v>2.621257936230549</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.526787497785769</v>
+        <v>2.576035060179485</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.676110283429132</v>
+        <v>2.749367393208829</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.877716197929978</v>
+        <v>2.977063523224551</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.252405155337506</v>
+        <v>2.352313191356181</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.759969427566645</v>
+        <v>2.88366604859489</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.023309636293192</v>
+        <v>3.171999184071019</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.565554224479769</v>
+        <v>2.737552984046431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.09074</t>
+          <t>X &lt; 0.09073</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2120</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.622857554371301</v>
+        <v>1.593661760018669</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.521105423571626</v>
+        <v>1.51991863712697</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.173503850137344</v>
+        <v>1.173350460133022</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7848610691974045</v>
+        <v>0.7843665768194015</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.001288497233787</v>
+        <v>1.049834416999559</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.204322904227361</v>
+        <v>1.228280313176974</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.921499337414026</v>
+        <v>1.969511016404347</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.73744956155182</v>
+        <v>1.786697123945537</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.723637216349793</v>
+        <v>1.79689432612949</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.581265589831261</v>
+        <v>1.680612915125835</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.18788518628805</v>
+        <v>1.287793222306725</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.646791640530154</v>
+        <v>1.770488261558398</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.934187957028072</v>
+        <v>2.0828775048059</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.688225494047053</v>
+        <v>1.860224253613715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.1059</t>
+          <t>X &lt; 0.1058</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2261</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.831335185741636</v>
+        <v>1.802139391389005</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.635452055968379</v>
+        <v>1.634265269523723</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.550278194433162</v>
+        <v>1.55012480442884</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.928623638773395</v>
+        <v>0.928129146395392</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.009529132117336</v>
+        <v>1.058075051883108</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.39535959695808</v>
+        <v>1.419317005907693</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.018300719337198</v>
+        <v>2.066312398327518</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.683916728358959</v>
+        <v>1.733164290752676</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.755619224644676</v>
+        <v>1.828876334424372</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.613351909960102</v>
+        <v>1.712699235254675</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.364422534097073</v>
+        <v>1.464330570115749</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.708398209672211</v>
+        <v>1.832094830700456</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.128583490812581</v>
+        <v>2.277273038590408</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.77935231220232</v>
+        <v>1.951351071768983</v>
       </c>
     </row>
     <row r="14">
@@ -4299,46 +4299,46 @@
         <v>2430</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.263939936543835</v>
+        <v>1.234744142191204</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8461694813400911</v>
+        <v>0.8449826948954353</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6571594134574852</v>
+        <v>0.6570060234531638</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4581664500499585</v>
+        <v>0.4576719576719555</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.537160847571549</v>
+        <v>0.5857067673373209</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7110780870831732</v>
+        <v>0.7350354960327863</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.079042624936349</v>
+        <v>1.12705430392667</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.064648878268947</v>
+        <v>1.113896440662664</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.168275775244119</v>
+        <v>1.241532885023815</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.9767931929060296</v>
+        <v>1.076140518200603</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8955488247692927</v>
+        <v>0.9954568607879679</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.259145084120497</v>
+        <v>1.382841705148742</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.826648551794747</v>
+        <v>1.975338099572575</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.640861568276428</v>
+        <v>1.81286032784309</v>
       </c>
     </row>
     <row r="15">
@@ -4351,46 +4351,46 @@
         <v>2573</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.075244093834094</v>
+        <v>1.046048299481463</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6688772778786927</v>
+        <v>0.6676904914340369</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5850269968935748</v>
+        <v>0.5848736068892535</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2100053468558158</v>
+        <v>0.2095108544778128</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1769625873862424</v>
+        <v>0.2255085071520142</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3966063410788507</v>
+        <v>0.4205637500284638</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6616822235538393</v>
+        <v>0.70969390254416</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6998603733932143</v>
+        <v>0.749107935786931</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6000130788992024</v>
+        <v>0.6732701886788988</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7217227318503348</v>
+        <v>0.8210700571449081</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.866807815331299</v>
+        <v>0.9667158513499743</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.095511657542829</v>
+        <v>1.219208278571074</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.608124115539162</v>
+        <v>1.75681366331699</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.445208386053309</v>
+        <v>1.617207145619972</v>
       </c>
     </row>
     <row r="16">
@@ -4403,46 +4403,46 @@
         <v>2705</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7538344315728551</v>
+        <v>0.7246386372202238</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5844228301910945</v>
+        <v>0.5832360437464388</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5593372125340252</v>
+        <v>0.5591838225297039</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.0980651287656471</v>
+        <v>0.09757063638764407</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.0335700805222956</v>
+        <v>0.01497583924347623</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1058818179851642</v>
+        <v>-0.08192440903555109</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2160621665564193</v>
+        <v>0.26407384554674</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2665535967068422</v>
+        <v>0.3158011591005589</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.01624002007471148</v>
+        <v>0.05701708970498487</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1689613314697311</v>
+        <v>0.2683086567643045</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1491030567585199</v>
+        <v>0.2490110927771951</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.442261246082424</v>
+        <v>0.5659578671106686</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8354190803845327</v>
+        <v>0.9841086281623603</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7284375402228989</v>
+        <v>0.9004362997895612</v>
       </c>
     </row>
     <row r="17">
@@ -4452,49 +4452,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4685221717128343</v>
+        <v>0.4579247047933777</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2267181011209161</v>
+        <v>0.2446106333361584</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2532950309726161</v>
+        <v>0.2723689569287231</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1728460172576121</v>
+        <v>0.1915048421897723</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1612418574203502</v>
+        <v>0.229126091121941</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1777170106509374</v>
+        <v>0.2209140686693516</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3739055277892689</v>
+        <v>0.4061308280564688</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2930728390587092</v>
+        <v>0.3266696869214556</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.02141652523255999</v>
+        <v>0.07894892183102797</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1546437963184317</v>
+        <v>0.2386117354663426</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.0201673571593588</v>
+        <v>0.1047206732481314</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4056691050203014</v>
+        <v>0.5141343372024068</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9686643191226239</v>
+        <v>1.102467805088878</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9135010929446636</v>
+        <v>1.070515125832735</v>
       </c>
     </row>
     <row r="18">
@@ -4507,46 +4507,46 @@
         <v>2951</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2808596387302984</v>
+        <v>0.2516638443776671</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.05903308480575475</v>
+        <v>0.057846298361099</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.00312988032858641</v>
+        <v>0.002976490324265058</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.09946820588915273</v>
+        <v>0.0989737135111497</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.06948092321027843</v>
+        <v>0.1180268429760503</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.02798677256748761</v>
+        <v>0.05194418151710067</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2482577755514015</v>
+        <v>0.2962694545417222</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1539441300703146</v>
+        <v>0.2031916924640313</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1103589346191711</v>
+        <v>-0.03710182483947477</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.04533364419878438</v>
+        <v>0.05401368109578897</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2839216204867654</v>
+        <v>-0.1840135844680901</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.01233574193692988</v>
+        <v>0.1113608790913148</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4146838554443377</v>
+        <v>0.5633734032221653</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3354381434207951</v>
+        <v>0.5074369029874575</v>
       </c>
     </row>
     <row r="19">
@@ -4556,49 +4556,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3075</v>
+        <v>3082</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3896645727741159</v>
+        <v>0.3604687784214846</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.238095735629841</v>
+        <v>0.2369089491851852</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2503101386292599</v>
+        <v>0.2324022291156993</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2684733489644486</v>
+        <v>0.2325425142486424</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3648023418797095</v>
+        <v>0.3595762146849708</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3228648223948625</v>
+        <v>0.2755664042791253</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4834177603056418</v>
+        <v>0.4419618881967082</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4567669559754393</v>
+        <v>0.3977963350790148</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.07378408551246451</v>
+        <v>-0.1257153593643068</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.06024384413100137</v>
+        <v>-0.1062095256479836</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3299856527977099</v>
+        <v>-0.3752218512249499</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1004855492228742</v>
+        <v>-0.1224394797374444</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2923717275450244</v>
+        <v>0.2933010692095976</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2579447761455356</v>
+        <v>0.3012023002141859</v>
       </c>
     </row>
     <row r="20">
@@ -4608,49 +4608,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3225</v>
+        <v>3233</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.34752291846101</v>
+        <v>0.2985301504216622</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4224309623634781</v>
+        <v>0.3820197319324663</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.322900695172919</v>
+        <v>0.2660595213955403</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3463219322648499</v>
+        <v>0.3033509700176324</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1654149140800243</v>
+        <v>0.1227438043743589</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2631172263256119</v>
+        <v>0.241208335538964</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.195396858113817</v>
+        <v>0.1805522463135034</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.364907418510974</v>
+        <v>0.3491173910906511</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.05073409645314797</v>
+        <v>-0.07221308934943238</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1083860380760555</v>
+        <v>0.07864626769430316</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2029294985152319</v>
+        <v>-0.2317860393020723</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.01749516546799867</v>
+        <v>-0.001769765329122208</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3105226067282345</v>
+        <v>0.3006929328639103</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.257188489512906</v>
+        <v>0.2889282437157945</v>
       </c>
     </row>
     <row r="21">
@@ -4660,101 +4660,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3321</v>
+        <v>3331</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3985080846426143</v>
+        <v>0.3359037533035476</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4833554221564</v>
+        <v>0.4303779563442163</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4350952791617857</v>
+        <v>0.3961366726430597</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4317034815275491</v>
+        <v>0.4061884789865573</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.0600170370944042</v>
+        <v>0.03677157290582045</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1636256581848698</v>
+        <v>0.1597667981357702</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1554661371237529</v>
+        <v>0.1290687676281053</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2759651940838168</v>
+        <v>0.2789876798057875</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.008881872816182579</v>
+        <v>-0.01116865744591422</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-9.346819115307881e-05</v>
+        <v>-0.008872530830437597</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3684347737510052</v>
+        <v>-0.3761947348188315</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1366757877427673</v>
+        <v>-0.1512746694516736</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.09220824487467638</v>
+        <v>0.07060089604919284</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.09413869364026795</v>
+        <v>0.06644030296146752</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.242</t>
+          <t>X &lt; 0.2419</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3415</v>
+        <v>3425</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2320361281587608</v>
+        <v>0.1827557151421288</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6204744740090504</v>
+        <v>0.5660005483147614</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4751813661359776</v>
+        <v>0.4212166204306911</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5046655038482797</v>
+        <v>0.4637135366817873</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1576321755973922</v>
+        <v>0.1492386456570429</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2081620831446784</v>
+        <v>0.2181208728942607</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3148034848286443</v>
+        <v>0.3191173848786448</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3607418792565582</v>
+        <v>0.3647837151258386</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.05283284693570067</v>
+        <v>0.05243643515639462</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1257754597590122</v>
+        <v>0.1195934199212232</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2380286770547499</v>
+        <v>-0.2432166629886297</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.01760406011922555</v>
+        <v>0.006348329498351291</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1993993926694486</v>
+        <v>0.1821516459463481</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1489564534658285</v>
+        <v>0.1265787502395241</v>
       </c>
     </row>
     <row r="23">
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3513</v>
+        <v>3524</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1849943494996822</v>
+        <v>0.1765397588234237</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4610893657635273</v>
+        <v>0.4470222639317072</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4790742782529094</v>
+        <v>0.4648689703464726</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4262071560980445</v>
+        <v>0.4121750030326297</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2725805375625043</v>
+        <v>0.262580546484898</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3584145269974854</v>
+        <v>0.352780836692439</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.431362116144733</v>
+        <v>0.4209625801817793</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4914641561782886</v>
+        <v>0.4806412150246899</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1336203757349494</v>
+        <v>0.1193786474135194</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1524374183085726</v>
+        <v>0.1332077895535875</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1500417031875543</v>
+        <v>-0.168439291294554</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.09944737471519005</v>
+        <v>0.0757729927734232</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2929362522568582</v>
+        <v>0.263929291237055</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2217586243608807</v>
+        <v>0.1885604067844326</v>
       </c>
     </row>
     <row r="24">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3571</v>
+        <v>3582</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.2534589694656475</v>
+        <v>0.2576211375608608</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3873843402589259</v>
+        <v>0.3863994594618916</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4545000259851335</v>
+        <v>0.4531345266354947</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4883669940734521</v>
+        <v>0.4869551384027986</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3285257692902874</v>
+        <v>0.3193000097024949</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.417803532841873</v>
+        <v>0.4124659441224736</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4882120577067965</v>
+        <v>0.4785822350651401</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4000001336028092</v>
+        <v>0.3904286399001791</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1867666747939296</v>
+        <v>0.1737767790122859</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1635323796452113</v>
+        <v>0.1461865821116959</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.02543744783048396</v>
+        <v>-0.04230335409916819</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1366315826537345</v>
+        <v>0.1152279852780751</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.320166955105357</v>
+        <v>0.2939528659189108</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2258160426487379</v>
+        <v>0.1959279292244815</v>
       </c>
     </row>
     <row r="25">
@@ -4868,153 +4868,153 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3638</v>
+        <v>3649</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.244364714467018</v>
+        <v>0.2479438823768092</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4010485613333188</v>
+        <v>0.4000189293453147</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5419014984979711</v>
+        <v>0.54029550601404</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4953253194456764</v>
+        <v>0.4939093429117989</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4107928197319879</v>
+        <v>0.4023778214787583</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5039171869253849</v>
+        <v>0.4988572888400924</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5166283588183873</v>
+        <v>0.5079693789822741</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4489007969762966</v>
+        <v>0.4402603482699305</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2659307853034321</v>
+        <v>0.2542840050546289</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2824250191309403</v>
+        <v>0.2668614882810019</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1206633469633758</v>
+        <v>0.1054997258509118</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2529496334806041</v>
+        <v>0.2338583385081208</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3979220328419757</v>
+        <v>0.3746841731956607</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.336975066173558</v>
+        <v>0.3104587453586802</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.3025</t>
+          <t>X &lt; 0.3024</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3694</v>
+        <v>3705</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1492431278147137</v>
+        <v>0.1526100686041403</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4950538397045676</v>
+        <v>0.4937436430914133</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5738552365860485</v>
+        <v>0.5721765462064994</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5299607065094349</v>
+        <v>0.5284560661411248</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.4385754496792771</v>
+        <v>0.4309370272148598</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5618094234979267</v>
+        <v>0.5570156591566899</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5190226992795033</v>
+        <v>0.5112115694297259</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.553359811424329</v>
+        <v>0.5452832752651631</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.3346301751860921</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4297507475401687</v>
+        <v>0.4154852552266561</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2132805859236413</v>
+        <v>0.1995800778561687</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5064461369771109</v>
+        <v>0.4887596603908051</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6158587513191875</v>
+        <v>0.5945719523616262</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.5593168098983554</v>
+        <v>0.5351408629891168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.3176</t>
+          <t>X &lt; 0.3175</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3731</v>
+        <v>3742</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1633147386964211</v>
+        <v>0.1663195998799978</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5165006014886515</v>
+        <v>0.5151287777568427</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6173488326409071</v>
+        <v>0.6155577006299424</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5484572219766548</v>
+        <v>0.5469083155650267</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5061316008560226</v>
+        <v>0.4988492709001591</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5508715223121143</v>
+        <v>0.5463935207241519</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4274100756758372</v>
+        <v>0.4204186798315774</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4299988266772061</v>
+        <v>0.4228502420865254</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1697606053037788</v>
+        <v>0.160503452424237</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3520720862572162</v>
+        <v>0.3391568714465336</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1892596039291021</v>
+        <v>0.1767520856968972</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.426277511067795</v>
+        <v>0.4102237880863839</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6108042687836104</v>
+        <v>0.5912125604317424</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5302578289463966</v>
+        <v>0.5081070324727719</v>
       </c>
     </row>
     <row r="28">
@@ -5024,49 +5024,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3776</v>
+        <v>3787</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1187144788348675</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4485525754514441</v>
+        <v>0.4473796869563742</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.5698996630225395</v>
+        <v>0.568265360726194</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4505359986794133</v>
+        <v>0.4492832687460009</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3230277360364084</v>
+        <v>0.3169378227692903</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3971506995123804</v>
+        <v>0.3934554443078042</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.24767552781897</v>
+        <v>0.2418576212720112</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2975106253794806</v>
+        <v>0.2914153486792799</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.09250489136837814</v>
+        <v>0.08445104932031455</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1831423992552317</v>
+        <v>0.1720499332870205</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.07271046201737619</v>
+        <v>0.06187596238737569</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3072838646279621</v>
+        <v>0.2932353397440153</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4580988176991667</v>
+        <v>0.4409496691381491</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.407645065521308</v>
+        <v>0.3881574510966672</v>
       </c>
     </row>
     <row r="29">
@@ -5076,49 +5076,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3833</v>
+        <v>3843</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.0931869335842137</v>
+        <v>0.1091827809221471</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.3682359778322493</v>
+        <v>0.3814192611633871</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4038653053824746</v>
+        <v>0.4169689501115812</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3141817159012845</v>
+        <v>0.3275184457380149</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2846560436178507</v>
+        <v>0.2937949177930648</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3100122638182725</v>
+        <v>0.32122603176024</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2656424191750304</v>
+        <v>0.2748283405895933</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.281758958161582</v>
+        <v>0.290915323232781</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.130998558243661</v>
+        <v>0.1124123114588045</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1294877169844426</v>
+        <v>0.134762436193455</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.0176410247203691</v>
+        <v>-0.002790476512934958</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2231489257137937</v>
+        <v>0.2000218386126491</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3393709768802324</v>
+        <v>0.3137887018687096</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3190826481556215</v>
+        <v>0.2913830868758609</v>
       </c>
     </row>
     <row r="30">
@@ -5128,153 +5128,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3863</v>
+        <v>3874</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.02166394882581102</v>
+        <v>0.02397616070602027</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2820914247889164</v>
+        <v>0.2813894224327171</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3918048602580342</v>
+        <v>0.390707979377332</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3038215551938279</v>
+        <v>0.3030013241135734</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3478306771807738</v>
+        <v>0.3428946359510618</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2978119836422692</v>
+        <v>0.2950179411260052</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3823252357125</v>
+        <v>0.3773323812539005</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.3430323994944402</v>
+        <v>0.3380490010122514</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2705436181760987</v>
+        <v>0.2638085765441573</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.159047596262063</v>
+        <v>0.1505011088066794</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.04648800329943725</v>
+        <v>0.0382129691446238</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1730554009343663</v>
+        <v>0.1624796161936004</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2851001020337378</v>
+        <v>0.2721653928156371</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2149351097040579</v>
+        <v>0.2002949718027054</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.3781</t>
+          <t>X &lt; 0.378</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3885</v>
+        <v>3896</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.007539587731422159</v>
+        <v>0.00971421757911628</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2060759621087698</v>
+        <v>0.2055851943583917</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3129211528377525</v>
+        <v>0.3120516785556902</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2518240357486192</v>
+        <v>0.2511520737327189</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.292529981471759</v>
+        <v>0.2880510236721818</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2187731269299391</v>
+        <v>0.2163525371175865</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.379390706259656</v>
+        <v>0.3747048924261804</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.337678439998939</v>
+        <v>0.3330158961281526</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2652533583685184</v>
+        <v>0.2589843562620615</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1495787323668054</v>
+        <v>0.1416675837276671</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.02243629953487414</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.05963124618227766</v>
+        <v>0.05013336257779599</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1171670110099541</v>
+        <v>0.1056187523063912</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.07437444623374745</v>
+        <v>0.06118508426731495</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.3932</t>
+          <t>X &lt; 0.3931</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3907</v>
+        <v>3917</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.006426234615986459</v>
+        <v>-0.01647314804220201</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1564306653785934</v>
+        <v>0.1444306114639105</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1838768744951693</v>
+        <v>0.1972908205833903</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1493511246402974</v>
+        <v>0.1628469569646001</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1867781189116684</v>
+        <v>0.1969090716963606</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1406225740989271</v>
+        <v>0.1525081704056674</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3253905455589603</v>
+        <v>0.3351563917433396</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3068288439631246</v>
+        <v>0.3166775490149121</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2088978560843273</v>
+        <v>0.2173430767669231</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.08907857980149458</v>
+        <v>0.09623176476468842</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.02453579523007932</v>
+        <v>-0.01707778269905447</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.02422977314140695</v>
+        <v>0.02989935506993646</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.02789028027405749</v>
+        <v>0.03191773518913266</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03900816011021391</v>
+        <v>-0.03649108012744051</v>
       </c>
     </row>
     <row r="33">
@@ -5284,49 +5284,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3936</v>
+        <v>3947</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0119365420562545</v>
+        <v>-0.01011182488698381</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.01408793920101914</v>
+        <v>-0.0139759522252092</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1622270743678342</v>
+        <v>0.1617856332240635</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1795908648347364</v>
+        <v>0.1791219899635337</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1874448451305781</v>
+        <v>0.1839416722793317</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1438154221193599</v>
+        <v>0.1419434575130225</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.275879442592057</v>
+        <v>0.2721613060560983</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2286378291681004</v>
+        <v>0.2249742385324964</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1055846197959056</v>
+        <v>0.1007863129906923</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.0196347070751699</v>
+        <v>-0.02569024194450975</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.133947287235074</v>
+        <v>-0.1397205106763195</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0345282517626444</v>
+        <v>-0.04204369064348867</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.008604419122718809</v>
+        <v>-0.01773230957348204</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.04794953279755276</v>
+        <v>-0.05840513292776706</v>
       </c>
     </row>
     <row r="34">
@@ -5336,101 +5336,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3969</v>
+        <v>3980</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01984119376891158</v>
+        <v>-0.01825106856340852</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.0149061657763454</v>
+        <v>0.01492752282289445</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.06086518511411754</v>
+        <v>0.06070549953772542</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07913952163875848</v>
+        <v>0.07894736842104066</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05729938731793283</v>
+        <v>0.05458569054898987</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.06675595084921326</v>
+        <v>0.06531027097490494</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07124687926892648</v>
+        <v>0.06852147965518895</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09594012758955728</v>
+        <v>0.09308078752277282</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.07402321591299454</v>
+        <v>0.06995841078657605</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1327331469248705</v>
+        <v>-0.1376033461456743</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1974726962482052</v>
+        <v>-0.2021948875374733</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1489753113806245</v>
+        <v>-0.1550872054014079</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1519771491931152</v>
+        <v>-0.1594006750389312</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1639591254331592</v>
+        <v>-0.1725812835058349</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.4386</t>
+          <t>X &lt; 0.4385</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4007</v>
+        <v>4018</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01822946337017584</v>
+        <v>-0.0169339533910744</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05071947381411235</v>
+        <v>0.05063168549066432</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.01785521240336863</v>
+        <v>0.01781301229026155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.03717787372157488</v>
+        <v>0.03709746063270813</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.01445983021115183</v>
+        <v>-0.0164938108586199</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.05299048325002076</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.04849248366502934</v>
+        <v>-0.05041163682430039</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.02848567722405448</v>
+        <v>-0.03051282391447074</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.0239720608728291</v>
+        <v>0.02077446814310946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1888900670180647</v>
+        <v>-0.1926220285331084</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2300322841867128</v>
+        <v>-0.2336766082526509</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1567329762518952</v>
+        <v>-0.1615965971668345</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1636917552454875</v>
+        <v>-0.1696071553226375</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1484659562922133</v>
+        <v>-0.1554223179463321</v>
       </c>
     </row>
   </sheetData>
